--- a/docs/SCI_SE_8.1.ProjectTestCaseSprint1_update.xlsx
+++ b/docs/SCI_SE_8.1.ProjectTestCaseSprint1_update.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F75C0D-9268-49F9-B59D-172DC5B6F280}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97787AF0-E254-47C8-9123-A7CEF9386CE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trường hợp kiểm thử" sheetId="1" r:id="rId1"/>
@@ -33,17 +33,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4127,15 +4116,291 @@
     <xf numFmtId="0" fontId="17" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="15" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="33" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4145,284 +4410,8 @@
     <xf numFmtId="0" fontId="31" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="31" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="15" fontId="6" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="40" fillId="8" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5716,28 +5705,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="218" t="s">
+      <c r="A1" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="219"/>
-      <c r="C1" s="219"/>
-      <c r="D1" s="220"/>
+      <c r="B1" s="210"/>
+      <c r="C1" s="210"/>
+      <c r="D1" s="211"/>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="221"/>
-      <c r="B2" s="222"/>
-      <c r="C2" s="222"/>
-      <c r="D2" s="223"/>
+      <c r="A2" s="212"/>
+      <c r="B2" s="213"/>
+      <c r="C2" s="213"/>
+      <c r="D2" s="214"/>
     </row>
     <row r="3" spans="1:5" s="197" customFormat="1">
       <c r="A3" s="199" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="224" t="s">
+      <c r="B3" s="215" t="s">
         <v>661</v>
       </c>
-      <c r="C3" s="225"/>
-      <c r="D3" s="226"/>
+      <c r="C3" s="216"/>
+      <c r="D3" s="217"/>
     </row>
     <row r="4" spans="1:5" s="197" customFormat="1">
       <c r="A4" s="198" t="s">
@@ -5791,10 +5780,10 @@
       </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="217">
+      <c r="A7" s="207">
         <v>3</v>
       </c>
-      <c r="B7" s="216" t="s">
+      <c r="B7" s="208" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="178" t="s">
@@ -5803,37 +5792,37 @@
       <c r="D7" s="142">
         <v>14</v>
       </c>
-      <c r="E7" s="213" t="s">
+      <c r="E7" s="218" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="217"/>
-      <c r="B8" s="216"/>
+      <c r="A8" s="207"/>
+      <c r="B8" s="208"/>
       <c r="C8" s="179" t="s">
         <v>14</v>
       </c>
       <c r="D8" s="142">
         <v>18</v>
       </c>
-      <c r="E8" s="214"/>
+      <c r="E8" s="219"/>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="217"/>
-      <c r="B9" s="216"/>
+      <c r="A9" s="207"/>
+      <c r="B9" s="208"/>
       <c r="C9" s="179" t="s">
         <v>15</v>
       </c>
       <c r="D9" s="142">
         <v>18</v>
       </c>
-      <c r="E9" s="215"/>
+      <c r="E9" s="220"/>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="217">
+      <c r="A10" s="207">
         <v>4</v>
       </c>
-      <c r="B10" s="216" t="s">
+      <c r="B10" s="208" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="179" t="s">
@@ -5842,37 +5831,37 @@
       <c r="D10" s="142">
         <v>16</v>
       </c>
-      <c r="E10" s="213" t="s">
+      <c r="E10" s="218" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:5">
-      <c r="A11" s="217"/>
-      <c r="B11" s="216"/>
+      <c r="A11" s="207"/>
+      <c r="B11" s="208"/>
       <c r="C11" s="179" t="s">
         <v>18</v>
       </c>
       <c r="D11" s="142">
         <v>15</v>
       </c>
-      <c r="E11" s="214"/>
+      <c r="E11" s="219"/>
     </row>
     <row r="12" spans="1:5">
-      <c r="A12" s="217"/>
-      <c r="B12" s="216"/>
+      <c r="A12" s="207"/>
+      <c r="B12" s="208"/>
       <c r="C12" s="179" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="142">
         <v>16</v>
       </c>
-      <c r="E12" s="215"/>
+      <c r="E12" s="220"/>
     </row>
     <row r="13" spans="1:5">
-      <c r="A13" s="217">
+      <c r="A13" s="207">
         <v>5</v>
       </c>
-      <c r="B13" s="216" t="s">
+      <c r="B13" s="208" t="s">
         <v>20</v>
       </c>
       <c r="C13" s="179" t="s">
@@ -5881,37 +5870,37 @@
       <c r="D13" s="142">
         <v>20</v>
       </c>
-      <c r="E13" s="213" t="s">
+      <c r="E13" s="218" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5">
-      <c r="A14" s="217"/>
-      <c r="B14" s="216"/>
+      <c r="A14" s="207"/>
+      <c r="B14" s="208"/>
       <c r="C14" s="179" t="s">
         <v>23</v>
       </c>
       <c r="D14" s="142">
         <v>16</v>
       </c>
-      <c r="E14" s="214"/>
+      <c r="E14" s="219"/>
     </row>
     <row r="15" spans="1:5">
-      <c r="A15" s="217"/>
-      <c r="B15" s="216"/>
+      <c r="A15" s="207"/>
+      <c r="B15" s="208"/>
       <c r="C15" s="179" t="s">
         <v>24</v>
       </c>
       <c r="D15" s="142">
         <v>16</v>
       </c>
-      <c r="E15" s="215"/>
+      <c r="E15" s="220"/>
     </row>
     <row r="16" spans="1:5">
-      <c r="A16" s="217">
+      <c r="A16" s="207">
         <v>6</v>
       </c>
-      <c r="B16" s="216" t="s">
+      <c r="B16" s="208" t="s">
         <v>25</v>
       </c>
       <c r="C16" s="179" t="s">
@@ -5920,31 +5909,31 @@
       <c r="D16" s="142">
         <v>18</v>
       </c>
-      <c r="E16" s="213" t="s">
+      <c r="E16" s="218" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="217"/>
-      <c r="B17" s="216"/>
+      <c r="A17" s="207"/>
+      <c r="B17" s="208"/>
       <c r="C17" s="179" t="s">
         <v>28</v>
       </c>
       <c r="D17" s="142">
         <v>13</v>
       </c>
-      <c r="E17" s="214"/>
+      <c r="E17" s="219"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="217"/>
-      <c r="B18" s="216"/>
+      <c r="A18" s="207"/>
+      <c r="B18" s="208"/>
       <c r="C18" s="179" t="s">
         <v>29</v>
       </c>
       <c r="D18" s="142">
         <v>14</v>
       </c>
-      <c r="E18" s="215"/>
+      <c r="E18" s="220"/>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="144">
@@ -5971,6 +5960,11 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="E10:E12"/>
+    <mergeCell ref="E13:E15"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="B13:B15"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="B16:B18"/>
     <mergeCell ref="A16:A18"/>
@@ -5980,11 +5974,6 @@
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="A10:A12"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="E10:E12"/>
-    <mergeCell ref="E13:E15"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="B13:B15"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" location="'Đăng nhập'!A1" display="Đăng nhập" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -6032,26 +6021,26 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="22.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>666</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="16.8">
@@ -6115,62 +6104,62 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="16.8">
-      <c r="A31" s="281" t="s">
+      <c r="A31" s="270" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="277" t="s">
+      <c r="B31" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="277" t="s">
+      <c r="C31" s="273" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="277" t="s">
+      <c r="D31" s="273" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="284" t="s">
+      <c r="E31" s="274" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="277" t="s">
+      <c r="F31" s="273" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="275" t="s">
+      <c r="G31" s="276" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="275"/>
-      <c r="I31" s="275"/>
-      <c r="J31" s="275"/>
-      <c r="K31" s="275"/>
-      <c r="L31" s="275"/>
-      <c r="M31" s="275" t="s">
+      <c r="H31" s="276"/>
+      <c r="I31" s="276"/>
+      <c r="J31" s="276"/>
+      <c r="K31" s="276"/>
+      <c r="L31" s="276"/>
+      <c r="M31" s="276" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="16.8">
-      <c r="A32" s="282"/>
-      <c r="B32" s="277"/>
-      <c r="C32" s="277"/>
-      <c r="D32" s="277"/>
-      <c r="E32" s="284"/>
-      <c r="F32" s="277"/>
-      <c r="G32" s="275" t="s">
+      <c r="A32" s="271"/>
+      <c r="B32" s="273"/>
+      <c r="C32" s="273"/>
+      <c r="D32" s="273"/>
+      <c r="E32" s="274"/>
+      <c r="F32" s="273"/>
+      <c r="G32" s="276" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="275"/>
-      <c r="I32" s="275"/>
-      <c r="J32" s="275" t="s">
+      <c r="H32" s="276"/>
+      <c r="I32" s="276"/>
+      <c r="J32" s="276" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="275"/>
-      <c r="L32" s="275"/>
-      <c r="M32" s="276"/>
+      <c r="K32" s="276"/>
+      <c r="L32" s="276"/>
+      <c r="M32" s="277"/>
     </row>
     <row r="33" spans="1:13" ht="16.8">
-      <c r="A33" s="283"/>
-      <c r="B33" s="277"/>
-      <c r="C33" s="277"/>
-      <c r="D33" s="277"/>
-      <c r="E33" s="284"/>
-      <c r="F33" s="277"/>
+      <c r="A33" s="272"/>
+      <c r="B33" s="273"/>
+      <c r="C33" s="273"/>
+      <c r="D33" s="273"/>
+      <c r="E33" s="274"/>
+      <c r="F33" s="273"/>
       <c r="G33" s="95" t="s">
         <v>80</v>
       </c>
@@ -6189,24 +6178,24 @@
       <c r="L33" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="M33" s="276"/>
+      <c r="M33" s="277"/>
     </row>
     <row r="34" spans="1:13" ht="16.8">
-      <c r="A34" s="285" t="s">
+      <c r="A34" s="278" t="s">
         <v>361</v>
       </c>
-      <c r="B34" s="286"/>
-      <c r="C34" s="286"/>
-      <c r="D34" s="286"/>
-      <c r="E34" s="286"/>
-      <c r="F34" s="286"/>
-      <c r="G34" s="286"/>
-      <c r="H34" s="286"/>
-      <c r="I34" s="286"/>
-      <c r="J34" s="286"/>
-      <c r="K34" s="286"/>
-      <c r="L34" s="286"/>
-      <c r="M34" s="287"/>
+      <c r="B34" s="279"/>
+      <c r="C34" s="279"/>
+      <c r="D34" s="279"/>
+      <c r="E34" s="279"/>
+      <c r="F34" s="279"/>
+      <c r="G34" s="279"/>
+      <c r="H34" s="279"/>
+      <c r="I34" s="279"/>
+      <c r="J34" s="279"/>
+      <c r="K34" s="279"/>
+      <c r="L34" s="279"/>
+      <c r="M34" s="280"/>
     </row>
     <row r="35" spans="1:13" s="108" customFormat="1" ht="40.200000000000003" customHeight="1">
       <c r="A35" s="118" t="s">
@@ -6486,21 +6475,21 @@
       <c r="M43" s="118"/>
     </row>
     <row r="44" spans="1:13" ht="16.8">
-      <c r="A44" s="254" t="s">
+      <c r="A44" s="243" t="s">
         <v>379</v>
       </c>
-      <c r="B44" s="255"/>
-      <c r="C44" s="255"/>
-      <c r="D44" s="255"/>
-      <c r="E44" s="255"/>
-      <c r="F44" s="255"/>
-      <c r="G44" s="255"/>
-      <c r="H44" s="255"/>
-      <c r="I44" s="255"/>
-      <c r="J44" s="255"/>
-      <c r="K44" s="255"/>
-      <c r="L44" s="255"/>
-      <c r="M44" s="256"/>
+      <c r="B44" s="244"/>
+      <c r="C44" s="244"/>
+      <c r="D44" s="244"/>
+      <c r="E44" s="244"/>
+      <c r="F44" s="244"/>
+      <c r="G44" s="244"/>
+      <c r="H44" s="244"/>
+      <c r="I44" s="244"/>
+      <c r="J44" s="244"/>
+      <c r="K44" s="244"/>
+      <c r="L44" s="244"/>
+      <c r="M44" s="245"/>
     </row>
     <row r="45" spans="1:13" ht="84">
       <c r="A45" s="98" t="s">
@@ -6813,26 +6802,26 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="22.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>667</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="16.8">
@@ -6896,62 +6885,62 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="17.399999999999999">
-      <c r="A31" s="210" t="s">
+      <c r="A31" s="284" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="210" t="s">
+      <c r="B31" s="284" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="210" t="s">
+      <c r="C31" s="284" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="210" t="s">
+      <c r="D31" s="284" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="210" t="s">
+      <c r="E31" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="210" t="s">
+      <c r="F31" s="284" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="291" t="s">
+      <c r="G31" s="285" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="291"/>
-      <c r="I31" s="291"/>
-      <c r="J31" s="291"/>
-      <c r="K31" s="291"/>
-      <c r="L31" s="291"/>
-      <c r="M31" s="292" t="s">
+      <c r="H31" s="285"/>
+      <c r="I31" s="285"/>
+      <c r="J31" s="285"/>
+      <c r="K31" s="285"/>
+      <c r="L31" s="285"/>
+      <c r="M31" s="286" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17.399999999999999">
-      <c r="A32" s="210"/>
-      <c r="B32" s="210"/>
-      <c r="C32" s="210"/>
-      <c r="D32" s="210"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="210"/>
-      <c r="G32" s="291" t="s">
+      <c r="A32" s="284"/>
+      <c r="B32" s="284"/>
+      <c r="C32" s="284"/>
+      <c r="D32" s="284"/>
+      <c r="E32" s="284"/>
+      <c r="F32" s="284"/>
+      <c r="G32" s="285" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="291"/>
-      <c r="I32" s="291"/>
-      <c r="J32" s="291" t="s">
+      <c r="H32" s="285"/>
+      <c r="I32" s="285"/>
+      <c r="J32" s="285" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="291"/>
-      <c r="L32" s="291"/>
-      <c r="M32" s="293"/>
+      <c r="K32" s="285"/>
+      <c r="L32" s="285"/>
+      <c r="M32" s="287"/>
     </row>
     <row r="33" spans="1:14" ht="15.6">
-      <c r="A33" s="210"/>
-      <c r="B33" s="210"/>
-      <c r="C33" s="210"/>
-      <c r="D33" s="210"/>
-      <c r="E33" s="210"/>
-      <c r="F33" s="210"/>
+      <c r="A33" s="284"/>
+      <c r="B33" s="284"/>
+      <c r="C33" s="284"/>
+      <c r="D33" s="284"/>
+      <c r="E33" s="284"/>
+      <c r="F33" s="284"/>
       <c r="G33" s="107" t="s">
         <v>80</v>
       </c>
@@ -6970,24 +6959,24 @@
       <c r="L33" s="107" t="s">
         <v>82</v>
       </c>
-      <c r="M33" s="293"/>
+      <c r="M33" s="287"/>
     </row>
     <row r="34" spans="1:14" ht="15.6">
-      <c r="A34" s="294" t="s">
+      <c r="A34" s="288" t="s">
         <v>406</v>
       </c>
-      <c r="B34" s="295"/>
-      <c r="C34" s="295"/>
-      <c r="D34" s="295"/>
-      <c r="E34" s="295"/>
-      <c r="F34" s="295"/>
-      <c r="G34" s="295"/>
-      <c r="H34" s="295"/>
-      <c r="I34" s="295"/>
-      <c r="J34" s="295"/>
-      <c r="K34" s="295"/>
-      <c r="L34" s="295"/>
-      <c r="M34" s="296"/>
+      <c r="B34" s="289"/>
+      <c r="C34" s="289"/>
+      <c r="D34" s="289"/>
+      <c r="E34" s="289"/>
+      <c r="F34" s="289"/>
+      <c r="G34" s="289"/>
+      <c r="H34" s="289"/>
+      <c r="I34" s="289"/>
+      <c r="J34" s="289"/>
+      <c r="K34" s="289"/>
+      <c r="L34" s="289"/>
+      <c r="M34" s="290"/>
     </row>
     <row r="35" spans="1:14" ht="33.6">
       <c r="A35" s="112" t="s">
@@ -7342,21 +7331,21 @@
       <c r="N43" s="38"/>
     </row>
     <row r="44" spans="1:14" ht="16.8">
-      <c r="A44" s="288" t="s">
+      <c r="A44" s="281" t="s">
         <v>423</v>
       </c>
-      <c r="B44" s="289"/>
-      <c r="C44" s="289"/>
-      <c r="D44" s="289"/>
-      <c r="E44" s="289"/>
-      <c r="F44" s="289"/>
-      <c r="G44" s="289"/>
-      <c r="H44" s="289"/>
-      <c r="I44" s="289"/>
-      <c r="J44" s="289"/>
-      <c r="K44" s="289"/>
-      <c r="L44" s="289"/>
-      <c r="M44" s="290"/>
+      <c r="B44" s="282"/>
+      <c r="C44" s="282"/>
+      <c r="D44" s="282"/>
+      <c r="E44" s="282"/>
+      <c r="F44" s="282"/>
+      <c r="G44" s="282"/>
+      <c r="H44" s="282"/>
+      <c r="I44" s="282"/>
+      <c r="J44" s="282"/>
+      <c r="K44" s="282"/>
+      <c r="L44" s="282"/>
+      <c r="M44" s="283"/>
     </row>
     <row r="45" spans="1:14" ht="67.2">
       <c r="A45" s="88" t="s">
@@ -7782,25 +7771,25 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
     </row>
     <row r="2" spans="1:6" ht="16.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>668</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
     </row>
     <row r="3" spans="1:6" ht="16.8">
       <c r="A3" s="89"/>
@@ -7862,62 +7851,62 @@
       </c>
     </row>
     <row r="28" spans="1:13" ht="17.399999999999999">
-      <c r="A28" s="209" t="s">
+      <c r="A28" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="209" t="s">
+      <c r="B28" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="209" t="s">
+      <c r="C28" s="291" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="209" t="s">
+      <c r="D28" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="210" t="s">
+      <c r="E28" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="209" t="s">
+      <c r="F28" s="291" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="202" t="s">
+      <c r="G28" s="292" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="202"/>
-      <c r="I28" s="202"/>
-      <c r="J28" s="202"/>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="211" t="s">
+      <c r="H28" s="292"/>
+      <c r="I28" s="292"/>
+      <c r="J28" s="292"/>
+      <c r="K28" s="292"/>
+      <c r="L28" s="292"/>
+      <c r="M28" s="293" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="17.399999999999999">
-      <c r="A29" s="209"/>
-      <c r="B29" s="209"/>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="209"/>
-      <c r="G29" s="202" t="s">
+      <c r="A29" s="291"/>
+      <c r="B29" s="291"/>
+      <c r="C29" s="291"/>
+      <c r="D29" s="291"/>
+      <c r="E29" s="284"/>
+      <c r="F29" s="291"/>
+      <c r="G29" s="292" t="s">
         <v>49</v>
       </c>
-      <c r="H29" s="202"/>
-      <c r="I29" s="202"/>
-      <c r="J29" s="202" t="s">
+      <c r="H29" s="292"/>
+      <c r="I29" s="292"/>
+      <c r="J29" s="292" t="s">
         <v>50</v>
       </c>
-      <c r="K29" s="202"/>
-      <c r="L29" s="202"/>
-      <c r="M29" s="212"/>
+      <c r="K29" s="292"/>
+      <c r="L29" s="292"/>
+      <c r="M29" s="294"/>
     </row>
     <row r="30" spans="1:13" ht="15.6">
-      <c r="A30" s="209"/>
-      <c r="B30" s="209"/>
-      <c r="C30" s="209"/>
-      <c r="D30" s="209"/>
-      <c r="E30" s="210"/>
-      <c r="F30" s="209"/>
+      <c r="A30" s="291"/>
+      <c r="B30" s="291"/>
+      <c r="C30" s="291"/>
+      <c r="D30" s="291"/>
+      <c r="E30" s="284"/>
+      <c r="F30" s="291"/>
       <c r="G30" s="99" t="s">
         <v>80</v>
       </c>
@@ -7936,24 +7925,24 @@
       <c r="L30" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="M30" s="212"/>
+      <c r="M30" s="294"/>
     </row>
     <row r="31" spans="1:13" ht="15.6">
-      <c r="A31" s="203" t="s">
+      <c r="A31" s="295" t="s">
         <v>466</v>
       </c>
-      <c r="B31" s="204"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="204"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="204"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="204"/>
-      <c r="J31" s="204"/>
-      <c r="K31" s="204"/>
-      <c r="L31" s="204"/>
-      <c r="M31" s="205"/>
+      <c r="B31" s="296"/>
+      <c r="C31" s="296"/>
+      <c r="D31" s="296"/>
+      <c r="E31" s="296"/>
+      <c r="F31" s="296"/>
+      <c r="G31" s="296"/>
+      <c r="H31" s="296"/>
+      <c r="I31" s="296"/>
+      <c r="J31" s="296"/>
+      <c r="K31" s="296"/>
+      <c r="L31" s="296"/>
+      <c r="M31" s="297"/>
     </row>
     <row r="32" spans="1:13" ht="50.4">
       <c r="A32" s="101" t="s">
@@ -8229,21 +8218,21 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="16.95" customHeight="1">
-      <c r="A39" s="254" t="s">
+      <c r="A39" s="243" t="s">
         <v>477</v>
       </c>
-      <c r="B39" s="255"/>
-      <c r="C39" s="255"/>
-      <c r="D39" s="255"/>
-      <c r="E39" s="255"/>
-      <c r="F39" s="255"/>
-      <c r="G39" s="255"/>
-      <c r="H39" s="255"/>
-      <c r="I39" s="255"/>
-      <c r="J39" s="255"/>
-      <c r="K39" s="255"/>
-      <c r="L39" s="255"/>
-      <c r="M39" s="256"/>
+      <c r="B39" s="244"/>
+      <c r="C39" s="244"/>
+      <c r="D39" s="244"/>
+      <c r="E39" s="244"/>
+      <c r="F39" s="244"/>
+      <c r="G39" s="244"/>
+      <c r="H39" s="244"/>
+      <c r="I39" s="244"/>
+      <c r="J39" s="244"/>
+      <c r="K39" s="244"/>
+      <c r="L39" s="244"/>
+      <c r="M39" s="245"/>
     </row>
     <row r="40" spans="1:13" ht="149.25" customHeight="1">
       <c r="A40" s="88" t="s">
@@ -8544,6 +8533,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A39:M39"/>
+    <mergeCell ref="G28:L28"/>
+    <mergeCell ref="M28:M30"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:L29"/>
+    <mergeCell ref="A31:M31"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A28:A30"/>
@@ -8552,12 +8547,6 @@
     <mergeCell ref="D28:D30"/>
     <mergeCell ref="E28:E30"/>
     <mergeCell ref="F28:F30"/>
-    <mergeCell ref="A39:M39"/>
-    <mergeCell ref="G28:L28"/>
-    <mergeCell ref="M28:M30"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:L29"/>
-    <mergeCell ref="A31:M31"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="J32:J38 G32:G38 J40:J48 G40:G48" xr:uid="{00000000-0002-0000-0B00-000000000000}">
@@ -8598,25 +8587,25 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
     </row>
     <row r="2" spans="1:6" ht="16.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>669</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
     </row>
     <row r="3" spans="1:6" ht="16.8">
       <c r="A3" s="89"/>
@@ -8686,62 +8675,62 @@
       <c r="F13" s="7"/>
     </row>
     <row r="28" spans="1:13" ht="16.8">
-      <c r="A28" s="209" t="s">
+      <c r="A28" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="209" t="s">
+      <c r="B28" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="209" t="s">
+      <c r="C28" s="291" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="209" t="s">
+      <c r="D28" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="210" t="s">
+      <c r="E28" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F28" s="209" t="s">
+      <c r="F28" s="291" t="s">
         <v>77</v>
       </c>
-      <c r="G28" s="211" t="s">
+      <c r="G28" s="293" t="s">
         <v>78</v>
       </c>
-      <c r="H28" s="211"/>
-      <c r="I28" s="211"/>
-      <c r="J28" s="211"/>
-      <c r="K28" s="211"/>
-      <c r="L28" s="211"/>
-      <c r="M28" s="211" t="s">
+      <c r="H28" s="293"/>
+      <c r="I28" s="293"/>
+      <c r="J28" s="293"/>
+      <c r="K28" s="293"/>
+      <c r="L28" s="293"/>
+      <c r="M28" s="293" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="16.8">
-      <c r="A29" s="209"/>
-      <c r="B29" s="209"/>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="209"/>
-      <c r="G29" s="211" t="s">
+      <c r="A29" s="291"/>
+      <c r="B29" s="291"/>
+      <c r="C29" s="291"/>
+      <c r="D29" s="291"/>
+      <c r="E29" s="284"/>
+      <c r="F29" s="291"/>
+      <c r="G29" s="293" t="s">
         <v>49</v>
       </c>
-      <c r="H29" s="211"/>
-      <c r="I29" s="211"/>
-      <c r="J29" s="211" t="s">
+      <c r="H29" s="293"/>
+      <c r="I29" s="293"/>
+      <c r="J29" s="293" t="s">
         <v>50</v>
       </c>
-      <c r="K29" s="211"/>
-      <c r="L29" s="211"/>
-      <c r="M29" s="297"/>
+      <c r="K29" s="293"/>
+      <c r="L29" s="293"/>
+      <c r="M29" s="298"/>
     </row>
     <row r="30" spans="1:13" ht="15.6">
-      <c r="A30" s="209"/>
-      <c r="B30" s="209"/>
-      <c r="C30" s="209"/>
-      <c r="D30" s="209"/>
-      <c r="E30" s="210"/>
-      <c r="F30" s="209"/>
+      <c r="A30" s="291"/>
+      <c r="B30" s="291"/>
+      <c r="C30" s="291"/>
+      <c r="D30" s="291"/>
+      <c r="E30" s="284"/>
+      <c r="F30" s="291"/>
       <c r="G30" s="99" t="s">
         <v>80</v>
       </c>
@@ -8760,24 +8749,24 @@
       <c r="L30" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="M30" s="297"/>
+      <c r="M30" s="298"/>
     </row>
     <row r="31" spans="1:13" ht="15.6">
-      <c r="A31" s="203" t="s">
+      <c r="A31" s="295" t="s">
         <v>511</v>
       </c>
-      <c r="B31" s="204"/>
-      <c r="C31" s="204"/>
-      <c r="D31" s="204"/>
-      <c r="E31" s="204"/>
-      <c r="F31" s="204"/>
-      <c r="G31" s="204"/>
-      <c r="H31" s="204"/>
-      <c r="I31" s="204"/>
-      <c r="J31" s="204"/>
-      <c r="K31" s="204"/>
-      <c r="L31" s="204"/>
-      <c r="M31" s="205"/>
+      <c r="B31" s="296"/>
+      <c r="C31" s="296"/>
+      <c r="D31" s="296"/>
+      <c r="E31" s="296"/>
+      <c r="F31" s="296"/>
+      <c r="G31" s="296"/>
+      <c r="H31" s="296"/>
+      <c r="I31" s="296"/>
+      <c r="J31" s="296"/>
+      <c r="K31" s="296"/>
+      <c r="L31" s="296"/>
+      <c r="M31" s="297"/>
     </row>
     <row r="32" spans="1:13" ht="33.6">
       <c r="A32" s="101" t="s">
@@ -9092,21 +9081,21 @@
       </c>
     </row>
     <row r="40" spans="1:13" ht="16.8">
-      <c r="A40" s="254" t="s">
+      <c r="A40" s="243" t="s">
         <v>521</v>
       </c>
-      <c r="B40" s="255"/>
-      <c r="C40" s="255"/>
-      <c r="D40" s="255"/>
-      <c r="E40" s="255"/>
-      <c r="F40" s="255"/>
-      <c r="G40" s="255"/>
-      <c r="H40" s="255"/>
-      <c r="I40" s="255"/>
-      <c r="J40" s="255"/>
-      <c r="K40" s="255"/>
-      <c r="L40" s="255"/>
-      <c r="M40" s="256"/>
+      <c r="B40" s="244"/>
+      <c r="C40" s="244"/>
+      <c r="D40" s="244"/>
+      <c r="E40" s="244"/>
+      <c r="F40" s="244"/>
+      <c r="G40" s="244"/>
+      <c r="H40" s="244"/>
+      <c r="I40" s="244"/>
+      <c r="J40" s="244"/>
+      <c r="K40" s="244"/>
+      <c r="L40" s="244"/>
+      <c r="M40" s="245"/>
     </row>
     <row r="41" spans="1:13" ht="229.5" customHeight="1">
       <c r="A41" s="88" t="s">
@@ -9427,26 +9416,26 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="22.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>670</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="16.8">
@@ -9509,62 +9498,62 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="17.399999999999999">
-      <c r="A31" s="209" t="s">
+      <c r="A31" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="209" t="s">
+      <c r="B31" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="209" t="s">
+      <c r="C31" s="291" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="209" t="s">
+      <c r="D31" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="210" t="s">
+      <c r="E31" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="209" t="s">
+      <c r="F31" s="291" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="202" t="s">
+      <c r="G31" s="292" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="202"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="202"/>
-      <c r="M31" s="211" t="s">
+      <c r="H31" s="292"/>
+      <c r="I31" s="292"/>
+      <c r="J31" s="292"/>
+      <c r="K31" s="292"/>
+      <c r="L31" s="292"/>
+      <c r="M31" s="293" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17.399999999999999">
-      <c r="A32" s="209"/>
-      <c r="B32" s="209"/>
-      <c r="C32" s="209"/>
-      <c r="D32" s="209"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="209"/>
-      <c r="G32" s="202" t="s">
+      <c r="A32" s="291"/>
+      <c r="B32" s="291"/>
+      <c r="C32" s="291"/>
+      <c r="D32" s="291"/>
+      <c r="E32" s="284"/>
+      <c r="F32" s="291"/>
+      <c r="G32" s="292" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="202"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="202" t="s">
+      <c r="H32" s="292"/>
+      <c r="I32" s="292"/>
+      <c r="J32" s="292" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="202"/>
-      <c r="L32" s="202"/>
-      <c r="M32" s="212"/>
+      <c r="K32" s="292"/>
+      <c r="L32" s="292"/>
+      <c r="M32" s="294"/>
     </row>
     <row r="33" spans="1:14" ht="15.6">
-      <c r="A33" s="209"/>
-      <c r="B33" s="209"/>
-      <c r="C33" s="209"/>
-      <c r="D33" s="209"/>
-      <c r="E33" s="210"/>
-      <c r="F33" s="209"/>
+      <c r="A33" s="291"/>
+      <c r="B33" s="291"/>
+      <c r="C33" s="291"/>
+      <c r="D33" s="291"/>
+      <c r="E33" s="284"/>
+      <c r="F33" s="291"/>
       <c r="G33" s="99" t="s">
         <v>80</v>
       </c>
@@ -9583,24 +9572,24 @@
       <c r="L33" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="M33" s="212"/>
+      <c r="M33" s="294"/>
     </row>
     <row r="34" spans="1:14" ht="15.6">
-      <c r="A34" s="203" t="s">
+      <c r="A34" s="295" t="s">
         <v>544</v>
       </c>
-      <c r="B34" s="204"/>
-      <c r="C34" s="204"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="204"/>
-      <c r="F34" s="204"/>
-      <c r="G34" s="204"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="204"/>
-      <c r="J34" s="204"/>
-      <c r="K34" s="204"/>
-      <c r="L34" s="204"/>
-      <c r="M34" s="205"/>
+      <c r="B34" s="296"/>
+      <c r="C34" s="296"/>
+      <c r="D34" s="296"/>
+      <c r="E34" s="296"/>
+      <c r="F34" s="296"/>
+      <c r="G34" s="296"/>
+      <c r="H34" s="296"/>
+      <c r="I34" s="296"/>
+      <c r="J34" s="296"/>
+      <c r="K34" s="296"/>
+      <c r="L34" s="296"/>
+      <c r="M34" s="297"/>
     </row>
     <row r="35" spans="1:14" ht="33.6">
       <c r="A35" s="87" t="s">
@@ -9701,7 +9690,7 @@
       <c r="L37" s="78"/>
       <c r="M37" s="102"/>
     </row>
-    <row r="38" spans="1:14" ht="67.2">
+    <row r="38" spans="1:14" ht="50.4">
       <c r="A38" s="87" t="s">
         <v>553</v>
       </c>
@@ -9834,21 +9823,21 @@
       <c r="M41" s="175"/>
     </row>
     <row r="42" spans="1:14" ht="16.8">
-      <c r="A42" s="206" t="s">
+      <c r="A42" s="267" t="s">
         <v>561</v>
       </c>
-      <c r="B42" s="207"/>
-      <c r="C42" s="207"/>
-      <c r="D42" s="207"/>
-      <c r="E42" s="207"/>
-      <c r="F42" s="207"/>
-      <c r="G42" s="207"/>
-      <c r="H42" s="207"/>
-      <c r="I42" s="207"/>
-      <c r="J42" s="207"/>
-      <c r="K42" s="207"/>
-      <c r="L42" s="207"/>
-      <c r="M42" s="208"/>
+      <c r="B42" s="268"/>
+      <c r="C42" s="268"/>
+      <c r="D42" s="268"/>
+      <c r="E42" s="268"/>
+      <c r="F42" s="268"/>
+      <c r="G42" s="268"/>
+      <c r="H42" s="268"/>
+      <c r="I42" s="268"/>
+      <c r="J42" s="268"/>
+      <c r="K42" s="268"/>
+      <c r="L42" s="268"/>
+      <c r="M42" s="269"/>
       <c r="N42" s="38"/>
     </row>
     <row r="43" spans="1:14" ht="84">
@@ -10257,25 +10246,25 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
     </row>
     <row r="2" spans="1:6" ht="16.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>671</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
     </row>
     <row r="3" spans="1:6" ht="16.8">
       <c r="A3" s="89"/>
@@ -10338,62 +10327,62 @@
       </c>
     </row>
     <row r="27" spans="1:13" ht="17.399999999999999">
-      <c r="A27" s="209" t="s">
+      <c r="A27" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="209" t="s">
+      <c r="B27" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="209" t="s">
+      <c r="C27" s="291" t="s">
         <v>102</v>
       </c>
-      <c r="D27" s="209" t="s">
+      <c r="D27" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="E27" s="210" t="s">
+      <c r="E27" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F27" s="209" t="s">
+      <c r="F27" s="291" t="s">
         <v>77</v>
       </c>
-      <c r="G27" s="202" t="s">
+      <c r="G27" s="292" t="s">
         <v>78</v>
       </c>
-      <c r="H27" s="202"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="202"/>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="211" t="s">
+      <c r="H27" s="292"/>
+      <c r="I27" s="292"/>
+      <c r="J27" s="292"/>
+      <c r="K27" s="292"/>
+      <c r="L27" s="292"/>
+      <c r="M27" s="293" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="17.399999999999999">
-      <c r="A28" s="209"/>
-      <c r="B28" s="209"/>
-      <c r="C28" s="209"/>
-      <c r="D28" s="209"/>
-      <c r="E28" s="210"/>
-      <c r="F28" s="209"/>
-      <c r="G28" s="202" t="s">
+      <c r="A28" s="291"/>
+      <c r="B28" s="291"/>
+      <c r="C28" s="291"/>
+      <c r="D28" s="291"/>
+      <c r="E28" s="284"/>
+      <c r="F28" s="291"/>
+      <c r="G28" s="292" t="s">
         <v>49</v>
       </c>
-      <c r="H28" s="202"/>
-      <c r="I28" s="202"/>
-      <c r="J28" s="202" t="s">
+      <c r="H28" s="292"/>
+      <c r="I28" s="292"/>
+      <c r="J28" s="292" t="s">
         <v>50</v>
       </c>
-      <c r="K28" s="202"/>
-      <c r="L28" s="202"/>
-      <c r="M28" s="212"/>
+      <c r="K28" s="292"/>
+      <c r="L28" s="292"/>
+      <c r="M28" s="294"/>
     </row>
     <row r="29" spans="1:13" ht="15.6">
-      <c r="A29" s="209"/>
-      <c r="B29" s="209"/>
-      <c r="C29" s="209"/>
-      <c r="D29" s="209"/>
-      <c r="E29" s="210"/>
-      <c r="F29" s="209"/>
+      <c r="A29" s="291"/>
+      <c r="B29" s="291"/>
+      <c r="C29" s="291"/>
+      <c r="D29" s="291"/>
+      <c r="E29" s="284"/>
+      <c r="F29" s="291"/>
       <c r="G29" s="99" t="s">
         <v>80</v>
       </c>
@@ -10412,24 +10401,24 @@
       <c r="L29" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="M29" s="212"/>
+      <c r="M29" s="294"/>
     </row>
     <row r="30" spans="1:13" ht="15.6">
-      <c r="A30" s="203" t="s">
+      <c r="A30" s="295" t="s">
         <v>596</v>
       </c>
-      <c r="B30" s="204"/>
-      <c r="C30" s="204"/>
-      <c r="D30" s="204"/>
-      <c r="E30" s="204"/>
-      <c r="F30" s="204"/>
-      <c r="G30" s="204"/>
-      <c r="H30" s="204"/>
-      <c r="I30" s="204"/>
-      <c r="J30" s="204"/>
-      <c r="K30" s="204"/>
-      <c r="L30" s="204"/>
-      <c r="M30" s="205"/>
+      <c r="B30" s="296"/>
+      <c r="C30" s="296"/>
+      <c r="D30" s="296"/>
+      <c r="E30" s="296"/>
+      <c r="F30" s="296"/>
+      <c r="G30" s="296"/>
+      <c r="H30" s="296"/>
+      <c r="I30" s="296"/>
+      <c r="J30" s="296"/>
+      <c r="K30" s="296"/>
+      <c r="L30" s="296"/>
+      <c r="M30" s="297"/>
     </row>
     <row r="31" spans="1:13" ht="33.6">
       <c r="A31" s="87" t="s">
@@ -10630,24 +10619,24 @@
       <c r="M36" s="102"/>
     </row>
     <row r="37" spans="1:14" ht="16.8">
-      <c r="A37" s="206" t="s">
+      <c r="A37" s="267" t="s">
         <v>607</v>
       </c>
-      <c r="B37" s="207"/>
-      <c r="C37" s="207"/>
-      <c r="D37" s="207"/>
-      <c r="E37" s="207"/>
-      <c r="F37" s="207"/>
-      <c r="G37" s="207"/>
-      <c r="H37" s="207"/>
-      <c r="I37" s="207"/>
-      <c r="J37" s="207"/>
-      <c r="K37" s="207"/>
-      <c r="L37" s="207"/>
-      <c r="M37" s="208"/>
+      <c r="B37" s="268"/>
+      <c r="C37" s="268"/>
+      <c r="D37" s="268"/>
+      <c r="E37" s="268"/>
+      <c r="F37" s="268"/>
+      <c r="G37" s="268"/>
+      <c r="H37" s="268"/>
+      <c r="I37" s="268"/>
+      <c r="J37" s="268"/>
+      <c r="K37" s="268"/>
+      <c r="L37" s="268"/>
+      <c r="M37" s="269"/>
       <c r="N37" s="38"/>
     </row>
-    <row r="38" spans="1:14" ht="134.4">
+    <row r="38" spans="1:14" ht="117.6">
       <c r="A38" s="88" t="s">
         <v>608</v>
       </c>
@@ -10947,25 +10936,25 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
     </row>
     <row r="2" spans="1:6" ht="16.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>672</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
     </row>
     <row r="3" spans="1:6" ht="16.8">
       <c r="A3" s="89"/>
@@ -11028,62 +11017,62 @@
       </c>
     </row>
     <row r="26" spans="1:13" ht="17.399999999999999">
-      <c r="A26" s="209" t="s">
+      <c r="A26" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="209" t="s">
+      <c r="B26" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="209" t="s">
+      <c r="C26" s="291" t="s">
         <v>102</v>
       </c>
-      <c r="D26" s="209" t="s">
+      <c r="D26" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="E26" s="210" t="s">
+      <c r="E26" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F26" s="209" t="s">
+      <c r="F26" s="291" t="s">
         <v>77</v>
       </c>
-      <c r="G26" s="202" t="s">
+      <c r="G26" s="292" t="s">
         <v>78</v>
       </c>
-      <c r="H26" s="202"/>
-      <c r="I26" s="202"/>
-      <c r="J26" s="202"/>
-      <c r="K26" s="202"/>
-      <c r="L26" s="202"/>
-      <c r="M26" s="211" t="s">
+      <c r="H26" s="292"/>
+      <c r="I26" s="292"/>
+      <c r="J26" s="292"/>
+      <c r="K26" s="292"/>
+      <c r="L26" s="292"/>
+      <c r="M26" s="293" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="17.399999999999999">
-      <c r="A27" s="209"/>
-      <c r="B27" s="209"/>
-      <c r="C27" s="209"/>
-      <c r="D27" s="209"/>
-      <c r="E27" s="210"/>
-      <c r="F27" s="209"/>
-      <c r="G27" s="202" t="s">
+      <c r="A27" s="291"/>
+      <c r="B27" s="291"/>
+      <c r="C27" s="291"/>
+      <c r="D27" s="291"/>
+      <c r="E27" s="284"/>
+      <c r="F27" s="291"/>
+      <c r="G27" s="292" t="s">
         <v>49</v>
       </c>
-      <c r="H27" s="202"/>
-      <c r="I27" s="202"/>
-      <c r="J27" s="202" t="s">
+      <c r="H27" s="292"/>
+      <c r="I27" s="292"/>
+      <c r="J27" s="292" t="s">
         <v>50</v>
       </c>
-      <c r="K27" s="202"/>
-      <c r="L27" s="202"/>
-      <c r="M27" s="212"/>
+      <c r="K27" s="292"/>
+      <c r="L27" s="292"/>
+      <c r="M27" s="294"/>
     </row>
     <row r="28" spans="1:13" ht="15.6">
-      <c r="A28" s="209"/>
-      <c r="B28" s="209"/>
-      <c r="C28" s="209"/>
-      <c r="D28" s="209"/>
-      <c r="E28" s="210"/>
-      <c r="F28" s="209"/>
+      <c r="A28" s="291"/>
+      <c r="B28" s="291"/>
+      <c r="C28" s="291"/>
+      <c r="D28" s="291"/>
+      <c r="E28" s="284"/>
+      <c r="F28" s="291"/>
       <c r="G28" s="99" t="s">
         <v>80</v>
       </c>
@@ -11102,24 +11091,24 @@
       <c r="L28" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="M28" s="212"/>
+      <c r="M28" s="294"/>
     </row>
     <row r="29" spans="1:13" ht="15.6">
-      <c r="A29" s="203" t="s">
+      <c r="A29" s="295" t="s">
         <v>633</v>
       </c>
-      <c r="B29" s="204"/>
-      <c r="C29" s="204"/>
-      <c r="D29" s="204"/>
-      <c r="E29" s="204"/>
-      <c r="F29" s="204"/>
-      <c r="G29" s="204"/>
-      <c r="H29" s="204"/>
-      <c r="I29" s="204"/>
-      <c r="J29" s="204"/>
-      <c r="K29" s="204"/>
-      <c r="L29" s="204"/>
-      <c r="M29" s="205"/>
+      <c r="B29" s="296"/>
+      <c r="C29" s="296"/>
+      <c r="D29" s="296"/>
+      <c r="E29" s="296"/>
+      <c r="F29" s="296"/>
+      <c r="G29" s="296"/>
+      <c r="H29" s="296"/>
+      <c r="I29" s="296"/>
+      <c r="J29" s="296"/>
+      <c r="K29" s="296"/>
+      <c r="L29" s="296"/>
+      <c r="M29" s="297"/>
     </row>
     <row r="30" spans="1:13" ht="50.4">
       <c r="A30" s="87" t="s">
@@ -11353,21 +11342,21 @@
       <c r="M36" s="102"/>
     </row>
     <row r="37" spans="1:14" ht="16.8">
-      <c r="A37" s="206" t="s">
+      <c r="A37" s="267" t="s">
         <v>643</v>
       </c>
-      <c r="B37" s="207"/>
-      <c r="C37" s="207"/>
-      <c r="D37" s="207"/>
-      <c r="E37" s="207"/>
-      <c r="F37" s="207"/>
-      <c r="G37" s="207"/>
-      <c r="H37" s="207"/>
-      <c r="I37" s="207"/>
-      <c r="J37" s="207"/>
-      <c r="K37" s="207"/>
-      <c r="L37" s="207"/>
-      <c r="M37" s="208"/>
+      <c r="B37" s="268"/>
+      <c r="C37" s="268"/>
+      <c r="D37" s="268"/>
+      <c r="E37" s="268"/>
+      <c r="F37" s="268"/>
+      <c r="G37" s="268"/>
+      <c r="H37" s="268"/>
+      <c r="I37" s="268"/>
+      <c r="J37" s="268"/>
+      <c r="K37" s="268"/>
+      <c r="L37" s="268"/>
+      <c r="M37" s="269"/>
       <c r="N37" s="38"/>
     </row>
     <row r="38" spans="1:14" ht="117.6">
@@ -11666,26 +11655,26 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="22.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>673</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="16.8">
@@ -11749,62 +11738,62 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="17.399999999999999">
-      <c r="A31" s="209" t="s">
+      <c r="A31" s="291" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="209" t="s">
+      <c r="B31" s="291" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="209" t="s">
+      <c r="C31" s="291" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="209" t="s">
+      <c r="D31" s="291" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="210" t="s">
+      <c r="E31" s="284" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="209" t="s">
+      <c r="F31" s="291" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="202" t="s">
+      <c r="G31" s="292" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="202"/>
-      <c r="I31" s="202"/>
-      <c r="J31" s="202"/>
-      <c r="K31" s="202"/>
-      <c r="L31" s="202"/>
-      <c r="M31" s="211" t="s">
+      <c r="H31" s="292"/>
+      <c r="I31" s="292"/>
+      <c r="J31" s="292"/>
+      <c r="K31" s="292"/>
+      <c r="L31" s="292"/>
+      <c r="M31" s="293" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="17.399999999999999">
-      <c r="A32" s="209"/>
-      <c r="B32" s="209"/>
-      <c r="C32" s="209"/>
-      <c r="D32" s="209"/>
-      <c r="E32" s="210"/>
-      <c r="F32" s="209"/>
-      <c r="G32" s="202" t="s">
+      <c r="A32" s="291"/>
+      <c r="B32" s="291"/>
+      <c r="C32" s="291"/>
+      <c r="D32" s="291"/>
+      <c r="E32" s="284"/>
+      <c r="F32" s="291"/>
+      <c r="G32" s="292" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="202"/>
-      <c r="I32" s="202"/>
-      <c r="J32" s="202" t="s">
+      <c r="H32" s="292"/>
+      <c r="I32" s="292"/>
+      <c r="J32" s="292" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="202"/>
-      <c r="L32" s="202"/>
-      <c r="M32" s="212"/>
+      <c r="K32" s="292"/>
+      <c r="L32" s="292"/>
+      <c r="M32" s="294"/>
     </row>
     <row r="33" spans="1:14" ht="15.6">
-      <c r="A33" s="209"/>
-      <c r="B33" s="209"/>
-      <c r="C33" s="209"/>
-      <c r="D33" s="209"/>
-      <c r="E33" s="210"/>
-      <c r="F33" s="209"/>
+      <c r="A33" s="291"/>
+      <c r="B33" s="291"/>
+      <c r="C33" s="291"/>
+      <c r="D33" s="291"/>
+      <c r="E33" s="284"/>
+      <c r="F33" s="291"/>
       <c r="G33" s="99" t="s">
         <v>80</v>
       </c>
@@ -11823,24 +11812,24 @@
       <c r="L33" s="99" t="s">
         <v>82</v>
       </c>
-      <c r="M33" s="212"/>
+      <c r="M33" s="294"/>
     </row>
     <row r="34" spans="1:14" ht="15.6">
-      <c r="A34" s="203" t="s">
+      <c r="A34" s="295" t="s">
         <v>406</v>
       </c>
-      <c r="B34" s="204"/>
-      <c r="C34" s="204"/>
-      <c r="D34" s="204"/>
-      <c r="E34" s="204"/>
-      <c r="F34" s="204"/>
-      <c r="G34" s="204"/>
-      <c r="H34" s="204"/>
-      <c r="I34" s="204"/>
-      <c r="J34" s="204"/>
-      <c r="K34" s="204"/>
-      <c r="L34" s="204"/>
-      <c r="M34" s="205"/>
+      <c r="B34" s="296"/>
+      <c r="C34" s="296"/>
+      <c r="D34" s="296"/>
+      <c r="E34" s="296"/>
+      <c r="F34" s="296"/>
+      <c r="G34" s="296"/>
+      <c r="H34" s="296"/>
+      <c r="I34" s="296"/>
+      <c r="J34" s="296"/>
+      <c r="K34" s="296"/>
+      <c r="L34" s="296"/>
+      <c r="M34" s="297"/>
     </row>
     <row r="35" spans="1:14" ht="33.6">
       <c r="A35" s="101" t="s">
@@ -12195,23 +12184,23 @@
       <c r="N43" s="38"/>
     </row>
     <row r="44" spans="1:14" ht="16.8">
-      <c r="A44" s="206" t="s">
+      <c r="A44" s="267" t="s">
         <v>423</v>
       </c>
-      <c r="B44" s="207"/>
-      <c r="C44" s="207"/>
-      <c r="D44" s="207"/>
-      <c r="E44" s="207"/>
-      <c r="F44" s="207"/>
-      <c r="G44" s="207"/>
-      <c r="H44" s="207"/>
-      <c r="I44" s="207"/>
-      <c r="J44" s="207"/>
-      <c r="K44" s="207"/>
-      <c r="L44" s="207"/>
-      <c r="M44" s="208"/>
-    </row>
-    <row r="45" spans="1:14" ht="100.8">
+      <c r="B44" s="268"/>
+      <c r="C44" s="268"/>
+      <c r="D44" s="268"/>
+      <c r="E44" s="268"/>
+      <c r="F44" s="268"/>
+      <c r="G44" s="268"/>
+      <c r="H44" s="268"/>
+      <c r="I44" s="268"/>
+      <c r="J44" s="268"/>
+      <c r="K44" s="268"/>
+      <c r="L44" s="268"/>
+      <c r="M44" s="269"/>
+    </row>
+    <row r="45" spans="1:14" ht="84">
       <c r="A45" s="88" t="s">
         <v>424</v>
       </c>
@@ -12622,24 +12611,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" s="1" customFormat="1" ht="24.6">
-      <c r="A1" s="235" t="s">
+      <c r="A1" s="236" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="235"/>
-      <c r="C1" s="235"/>
-      <c r="D1" s="235"/>
-      <c r="E1" s="235"/>
-      <c r="F1" s="235"/>
-      <c r="G1" s="235"/>
-      <c r="H1" s="235"/>
-      <c r="I1" s="235"/>
-      <c r="J1" s="235"/>
-      <c r="K1" s="235"/>
-      <c r="L1" s="235"/>
-      <c r="M1" s="235"/>
-      <c r="N1" s="235"/>
-      <c r="O1" s="235"/>
-      <c r="P1" s="235"/>
+      <c r="B1" s="236"/>
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="236"/>
+      <c r="F1" s="236"/>
+      <c r="G1" s="236"/>
+      <c r="H1" s="236"/>
+      <c r="I1" s="236"/>
+      <c r="J1" s="236"/>
+      <c r="K1" s="236"/>
+      <c r="L1" s="236"/>
+      <c r="M1" s="236"/>
+      <c r="N1" s="236"/>
+      <c r="O1" s="236"/>
+      <c r="P1" s="236"/>
     </row>
     <row r="2" spans="1:16" s="1" customFormat="1" ht="13.2">
       <c r="A2" s="2"/>
@@ -12663,22 +12652,22 @@
       <c r="A3" s="147" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="236" t="s">
+      <c r="B3" s="237" t="s">
         <v>33</v>
       </c>
-      <c r="C3" s="236"/>
+      <c r="C3" s="237"/>
       <c r="D3" s="148"/>
-      <c r="E3" s="228" t="s">
+      <c r="E3" s="224" t="s">
         <v>34</v>
       </c>
-      <c r="F3" s="228"/>
-      <c r="G3" s="228"/>
-      <c r="H3" s="229" t="s">
+      <c r="F3" s="224"/>
+      <c r="G3" s="224"/>
+      <c r="H3" s="230" t="s">
         <v>35</v>
       </c>
-      <c r="I3" s="230"/>
-      <c r="J3" s="230"/>
-      <c r="K3" s="231"/>
+      <c r="I3" s="231"/>
+      <c r="J3" s="231"/>
+      <c r="K3" s="232"/>
       <c r="L3" s="149"/>
       <c r="M3" s="149"/>
       <c r="N3" s="149"/>
@@ -12687,20 +12676,20 @@
     </row>
     <row r="4" spans="1:16" s="1" customFormat="1" ht="16.8">
       <c r="A4" s="147"/>
-      <c r="B4" s="227"/>
-      <c r="C4" s="227"/>
+      <c r="B4" s="223"/>
+      <c r="C4" s="223"/>
       <c r="D4" s="150"/>
-      <c r="E4" s="228" t="s">
+      <c r="E4" s="224" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="228"/>
-      <c r="G4" s="228"/>
-      <c r="H4" s="232" t="s">
+      <c r="F4" s="224"/>
+      <c r="G4" s="224"/>
+      <c r="H4" s="233" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="233"/>
-      <c r="J4" s="233"/>
-      <c r="K4" s="234"/>
+      <c r="I4" s="234"/>
+      <c r="J4" s="234"/>
+      <c r="K4" s="235"/>
       <c r="L4" s="150"/>
       <c r="M4" s="149"/>
       <c r="N4" s="149"/>
@@ -12709,20 +12698,20 @@
     </row>
     <row r="5" spans="1:16" s="1" customFormat="1" ht="16.8">
       <c r="A5" s="147"/>
-      <c r="B5" s="227"/>
-      <c r="C5" s="227"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="223"/>
       <c r="D5" s="150"/>
-      <c r="E5" s="228" t="s">
+      <c r="E5" s="224" t="s">
         <v>38</v>
       </c>
-      <c r="F5" s="228"/>
-      <c r="G5" s="228"/>
-      <c r="H5" s="241">
+      <c r="F5" s="224"/>
+      <c r="G5" s="224"/>
+      <c r="H5" s="227">
         <v>44114</v>
       </c>
-      <c r="I5" s="242"/>
-      <c r="J5" s="242"/>
-      <c r="K5" s="243"/>
+      <c r="I5" s="228"/>
+      <c r="J5" s="228"/>
+      <c r="K5" s="229"/>
       <c r="L5" s="150"/>
       <c r="M5" s="149"/>
       <c r="N5" s="149"/>
@@ -12733,18 +12722,18 @@
       <c r="A6" s="151" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="239" t="s">
+      <c r="B6" s="225" t="s">
         <v>40</v>
       </c>
-      <c r="C6" s="239"/>
-      <c r="D6" s="239"/>
-      <c r="E6" s="239"/>
-      <c r="F6" s="239"/>
-      <c r="G6" s="239"/>
-      <c r="H6" s="239"/>
-      <c r="I6" s="239"/>
-      <c r="J6" s="239"/>
-      <c r="K6" s="239"/>
+      <c r="C6" s="225"/>
+      <c r="D6" s="225"/>
+      <c r="E6" s="225"/>
+      <c r="F6" s="225"/>
+      <c r="G6" s="225"/>
+      <c r="H6" s="225"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="225"/>
+      <c r="K6" s="225"/>
       <c r="L6" s="152"/>
       <c r="M6" s="153"/>
       <c r="N6" s="153"/>
@@ -12754,52 +12743,52 @@
     <row r="7" spans="1:16" s="1" customFormat="1" ht="20.25" customHeight="1">
       <c r="A7" s="154"/>
       <c r="B7" s="155"/>
-      <c r="C7" s="240" t="s">
+      <c r="C7" s="226" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="240"/>
-      <c r="E7" s="240" t="s">
+      <c r="D7" s="226"/>
+      <c r="E7" s="226" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="240"/>
-      <c r="G7" s="240" t="s">
+      <c r="F7" s="226"/>
+      <c r="G7" s="226" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="240"/>
-      <c r="I7" s="240" t="s">
+      <c r="H7" s="226"/>
+      <c r="I7" s="226" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="240"/>
-      <c r="K7" s="240" t="s">
+      <c r="J7" s="226"/>
+      <c r="K7" s="226" t="s">
         <v>45</v>
       </c>
-      <c r="L7" s="240"/>
-      <c r="M7" s="237" t="s">
+      <c r="L7" s="226"/>
+      <c r="M7" s="221" t="s">
         <v>46</v>
       </c>
-      <c r="N7" s="237"/>
-      <c r="O7" s="238" t="s">
+      <c r="N7" s="221"/>
+      <c r="O7" s="222" t="s">
         <v>47</v>
       </c>
-      <c r="P7" s="238"/>
+      <c r="P7" s="222"/>
     </row>
     <row r="8" spans="1:16" s="1" customFormat="1" ht="16.8">
       <c r="A8" s="156"/>
       <c r="B8" s="157"/>
-      <c r="C8" s="240"/>
-      <c r="D8" s="240"/>
-      <c r="E8" s="240"/>
-      <c r="F8" s="240"/>
-      <c r="G8" s="240"/>
-      <c r="H8" s="240"/>
-      <c r="I8" s="240"/>
-      <c r="J8" s="240"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="240"/>
-      <c r="M8" s="237"/>
-      <c r="N8" s="237"/>
-      <c r="O8" s="238"/>
-      <c r="P8" s="238"/>
+      <c r="C8" s="226"/>
+      <c r="D8" s="226"/>
+      <c r="E8" s="226"/>
+      <c r="F8" s="226"/>
+      <c r="G8" s="226"/>
+      <c r="H8" s="226"/>
+      <c r="I8" s="226"/>
+      <c r="J8" s="226"/>
+      <c r="K8" s="226"/>
+      <c r="L8" s="226"/>
+      <c r="M8" s="221"/>
+      <c r="N8" s="221"/>
+      <c r="O8" s="222"/>
+      <c r="P8" s="222"/>
     </row>
     <row r="9" spans="1:16" s="5" customFormat="1" ht="22.5" customHeight="1">
       <c r="A9" s="158" t="s">
@@ -13520,6 +13509,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="E4:G4"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="H4:K4"/>
+    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="E3:G3"/>
     <mergeCell ref="M7:N8"/>
     <mergeCell ref="O7:P8"/>
     <mergeCell ref="B5:C5"/>
@@ -13531,13 +13527,6 @@
     <mergeCell ref="I7:J8"/>
     <mergeCell ref="K7:L8"/>
     <mergeCell ref="H5:K5"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="H4:K4"/>
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="E3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
@@ -13569,13 +13558,13 @@
       <c r="A1" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="8"/>
       <c r="H1" s="9"/>
       <c r="J1" s="8"/>
@@ -13584,13 +13573,13 @@
       <c r="A2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="244" t="s">
+      <c r="B2" s="205" t="s">
         <v>662</v>
       </c>
-      <c r="C2" s="244"/>
-      <c r="D2" s="244"/>
-      <c r="E2" s="244"/>
-      <c r="F2" s="244"/>
+      <c r="C2" s="205"/>
+      <c r="D2" s="205"/>
+      <c r="E2" s="205"/>
+      <c r="F2" s="205"/>
       <c r="G2" s="8"/>
       <c r="H2" s="9"/>
       <c r="J2" s="8"/>
@@ -13679,64 +13668,64 @@
       <c r="J6" s="30"/>
     </row>
     <row r="7" spans="1:13" s="32" customFormat="1" ht="18">
-      <c r="A7" s="245" t="s">
+      <c r="A7" s="203" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="245" t="s">
+      <c r="B7" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="245" t="s">
+      <c r="C7" s="203" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="245" t="s">
+      <c r="D7" s="203" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="246" t="s">
+      <c r="E7" s="206" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="245" t="s">
+      <c r="F7" s="203" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="245" t="s">
+      <c r="G7" s="203" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="245"/>
-      <c r="I7" s="245"/>
-      <c r="J7" s="245" t="s">
+      <c r="H7" s="203"/>
+      <c r="I7" s="203"/>
+      <c r="J7" s="203" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="245"/>
-      <c r="L7" s="245"/>
-      <c r="M7" s="245" t="s">
+      <c r="K7" s="203"/>
+      <c r="L7" s="203"/>
+      <c r="M7" s="203" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="32" customFormat="1" ht="18">
-      <c r="A8" s="245"/>
-      <c r="B8" s="245"/>
-      <c r="C8" s="245"/>
-      <c r="D8" s="245"/>
-      <c r="E8" s="246"/>
-      <c r="F8" s="245"/>
-      <c r="G8" s="245" t="s">
+      <c r="A8" s="203"/>
+      <c r="B8" s="203"/>
+      <c r="C8" s="203"/>
+      <c r="D8" s="203"/>
+      <c r="E8" s="206"/>
+      <c r="F8" s="203"/>
+      <c r="G8" s="203" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="245"/>
-      <c r="I8" s="245"/>
-      <c r="J8" s="245" t="s">
+      <c r="H8" s="203"/>
+      <c r="I8" s="203"/>
+      <c r="J8" s="203" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="245"/>
-      <c r="L8" s="245"/>
-      <c r="M8" s="245"/>
+      <c r="K8" s="203"/>
+      <c r="L8" s="203"/>
+      <c r="M8" s="203"/>
     </row>
     <row r="9" spans="1:13" s="32" customFormat="1" ht="18">
-      <c r="A9" s="245"/>
-      <c r="B9" s="245"/>
-      <c r="C9" s="245"/>
-      <c r="D9" s="245"/>
-      <c r="E9" s="246"/>
-      <c r="F9" s="245"/>
+      <c r="A9" s="203"/>
+      <c r="B9" s="203"/>
+      <c r="C9" s="203"/>
+      <c r="D9" s="203"/>
+      <c r="E9" s="206"/>
+      <c r="F9" s="203"/>
       <c r="G9" s="85" t="s">
         <v>80</v>
       </c>
@@ -13755,24 +13744,24 @@
       <c r="L9" s="85" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="245"/>
+      <c r="M9" s="203"/>
     </row>
     <row r="10" spans="1:13" s="32" customFormat="1" ht="18">
-      <c r="A10" s="247" t="s">
+      <c r="A10" s="201" t="s">
         <v>674</v>
       </c>
-      <c r="B10" s="247"/>
-      <c r="C10" s="247"/>
-      <c r="D10" s="247"/>
-      <c r="E10" s="247"/>
-      <c r="F10" s="247"/>
-      <c r="G10" s="247"/>
-      <c r="H10" s="247"/>
-      <c r="I10" s="247"/>
-      <c r="J10" s="247"/>
-      <c r="K10" s="247"/>
-      <c r="L10" s="247"/>
-      <c r="M10" s="247"/>
+      <c r="B10" s="201"/>
+      <c r="C10" s="201"/>
+      <c r="D10" s="201"/>
+      <c r="E10" s="201"/>
+      <c r="F10" s="201"/>
+      <c r="G10" s="201"/>
+      <c r="H10" s="201"/>
+      <c r="I10" s="201"/>
+      <c r="J10" s="201"/>
+      <c r="K10" s="201"/>
+      <c r="L10" s="201"/>
+      <c r="M10" s="201"/>
     </row>
     <row r="11" spans="1:13" s="32" customFormat="1" ht="46.8" customHeight="1">
       <c r="A11" s="87" t="s">
@@ -13820,10 +13809,10 @@
       <c r="D12" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E12" s="298" t="s">
+      <c r="E12" s="200" t="s">
         <v>704</v>
       </c>
-      <c r="F12" s="298" t="s">
+      <c r="F12" s="200" t="s">
         <v>704</v>
       </c>
       <c r="G12" s="78" t="s">
@@ -13919,10 +13908,10 @@
       <c r="D15" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E15" s="298" t="s">
+      <c r="E15" s="200" t="s">
         <v>708</v>
       </c>
-      <c r="F15" s="298" t="s">
+      <c r="F15" s="200" t="s">
         <v>708</v>
       </c>
       <c r="G15" s="78" t="s">
@@ -13952,10 +13941,10 @@
       <c r="D16" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E16" s="298" t="s">
+      <c r="E16" s="200" t="s">
         <v>707</v>
       </c>
-      <c r="F16" s="298" t="s">
+      <c r="F16" s="200" t="s">
         <v>707</v>
       </c>
       <c r="G16" s="78" t="s">
@@ -13985,10 +13974,10 @@
       <c r="D17" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E17" s="298" t="s">
+      <c r="E17" s="200" t="s">
         <v>708</v>
       </c>
-      <c r="F17" s="298" t="s">
+      <c r="F17" s="200" t="s">
         <v>708</v>
       </c>
       <c r="G17" s="78" t="s">
@@ -14018,10 +14007,10 @@
       <c r="D18" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E18" s="298" t="s">
+      <c r="E18" s="200" t="s">
         <v>709</v>
       </c>
-      <c r="F18" s="298" t="s">
+      <c r="F18" s="200" t="s">
         <v>709</v>
       </c>
       <c r="G18" s="78" t="s">
@@ -14051,10 +14040,10 @@
       <c r="D19" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E19" s="298" t="s">
+      <c r="E19" s="200" t="s">
         <v>708</v>
       </c>
-      <c r="F19" s="298" t="s">
+      <c r="F19" s="200" t="s">
         <v>708</v>
       </c>
       <c r="G19" s="78" t="s">
@@ -14084,10 +14073,10 @@
       <c r="D20" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E20" s="298" t="s">
+      <c r="E20" s="200" t="s">
         <v>709</v>
       </c>
-      <c r="F20" s="298" t="s">
+      <c r="F20" s="200" t="s">
         <v>709</v>
       </c>
       <c r="G20" s="78" t="s">
@@ -14117,10 +14106,10 @@
       <c r="D21" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E21" s="298" t="s">
+      <c r="E21" s="200" t="s">
         <v>710</v>
       </c>
-      <c r="F21" s="298" t="s">
+      <c r="F21" s="200" t="s">
         <v>710</v>
       </c>
       <c r="G21" s="78" t="s">
@@ -14150,10 +14139,10 @@
       <c r="D22" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E22" s="298" t="s">
+      <c r="E22" s="200" t="s">
         <v>711</v>
       </c>
-      <c r="F22" s="298" t="s">
+      <c r="F22" s="200" t="s">
         <v>711</v>
       </c>
       <c r="G22" s="78" t="s">
@@ -14183,10 +14172,10 @@
       <c r="D23" s="90" t="s">
         <v>703</v>
       </c>
-      <c r="E23" s="298" t="s">
+      <c r="E23" s="200" t="s">
         <v>712</v>
       </c>
-      <c r="F23" s="298" t="s">
+      <c r="F23" s="200" t="s">
         <v>712</v>
       </c>
       <c r="G23" s="78" t="s">
@@ -14237,21 +14226,21 @@
       <c r="M24" s="89"/>
     </row>
     <row r="25" spans="1:13" s="32" customFormat="1" ht="18">
-      <c r="A25" s="248" t="s">
+      <c r="A25" s="202" t="s">
         <v>714</v>
       </c>
-      <c r="B25" s="248"/>
-      <c r="C25" s="248"/>
-      <c r="D25" s="248"/>
-      <c r="E25" s="248"/>
-      <c r="F25" s="248"/>
-      <c r="G25" s="248"/>
-      <c r="H25" s="248"/>
-      <c r="I25" s="248"/>
-      <c r="J25" s="248"/>
-      <c r="K25" s="248"/>
-      <c r="L25" s="248"/>
-      <c r="M25" s="248"/>
+      <c r="B25" s="202"/>
+      <c r="C25" s="202"/>
+      <c r="D25" s="202"/>
+      <c r="E25" s="202"/>
+      <c r="F25" s="202"/>
+      <c r="G25" s="202"/>
+      <c r="H25" s="202"/>
+      <c r="I25" s="202"/>
+      <c r="J25" s="202"/>
+      <c r="K25" s="202"/>
+      <c r="L25" s="202"/>
+      <c r="M25" s="202"/>
     </row>
     <row r="26" spans="1:13" s="32" customFormat="1" ht="35.4" customHeight="1">
       <c r="A26" s="88" t="s">
@@ -14645,13 +14634,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A10:M10"/>
-    <mergeCell ref="A25:M25"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="J8:L8"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A7:A9"/>
@@ -14660,6 +14642,13 @@
     <mergeCell ref="C7:C9"/>
     <mergeCell ref="E7:E9"/>
     <mergeCell ref="F7:F9"/>
+    <mergeCell ref="A10:M10"/>
+    <mergeCell ref="A25:M25"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="J8:L8"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <dataValidations count="1">
@@ -14699,13 +14688,13 @@
       <c r="A1" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="249" t="s">
+      <c r="B1" s="238" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="249"/>
-      <c r="D1" s="249"/>
-      <c r="E1" s="249"/>
-      <c r="F1" s="249"/>
+      <c r="C1" s="238"/>
+      <c r="D1" s="238"/>
+      <c r="E1" s="238"/>
+      <c r="F1" s="238"/>
       <c r="G1" s="42"/>
       <c r="H1" s="43"/>
       <c r="J1" s="42"/>
@@ -14714,13 +14703,13 @@
       <c r="A2" s="57" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="250" t="s">
+      <c r="B2" s="239" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="250"/>
-      <c r="D2" s="250"/>
-      <c r="E2" s="250"/>
-      <c r="F2" s="250"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
       <c r="G2" s="42"/>
       <c r="H2" s="43"/>
       <c r="J2" s="42"/>
@@ -14805,64 +14794,64 @@
       <c r="J6" s="42"/>
     </row>
     <row r="7" spans="1:13" s="44" customFormat="1">
-      <c r="A7" s="253" t="s">
+      <c r="A7" s="242" t="s">
         <v>73</v>
       </c>
-      <c r="B7" s="253" t="s">
+      <c r="B7" s="242" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="253" t="s">
+      <c r="C7" s="242" t="s">
         <v>74</v>
       </c>
-      <c r="D7" s="253" t="s">
+      <c r="D7" s="242" t="s">
         <v>75</v>
       </c>
-      <c r="E7" s="253" t="s">
+      <c r="E7" s="242" t="s">
         <v>76</v>
       </c>
-      <c r="F7" s="253" t="s">
+      <c r="F7" s="242" t="s">
         <v>77</v>
       </c>
-      <c r="G7" s="253" t="s">
+      <c r="G7" s="242" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="253"/>
-      <c r="I7" s="253"/>
-      <c r="J7" s="253" t="s">
+      <c r="H7" s="242"/>
+      <c r="I7" s="242"/>
+      <c r="J7" s="242" t="s">
         <v>78</v>
       </c>
-      <c r="K7" s="253"/>
-      <c r="L7" s="253"/>
-      <c r="M7" s="253" t="s">
+      <c r="K7" s="242"/>
+      <c r="L7" s="242"/>
+      <c r="M7" s="242" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:13" s="44" customFormat="1">
-      <c r="A8" s="253"/>
-      <c r="B8" s="253"/>
-      <c r="C8" s="253"/>
-      <c r="D8" s="253"/>
-      <c r="E8" s="253"/>
-      <c r="F8" s="253"/>
-      <c r="G8" s="253" t="s">
+      <c r="A8" s="242"/>
+      <c r="B8" s="242"/>
+      <c r="C8" s="242"/>
+      <c r="D8" s="242"/>
+      <c r="E8" s="242"/>
+      <c r="F8" s="242"/>
+      <c r="G8" s="242" t="s">
         <v>49</v>
       </c>
-      <c r="H8" s="253"/>
-      <c r="I8" s="253"/>
-      <c r="J8" s="253" t="s">
+      <c r="H8" s="242"/>
+      <c r="I8" s="242"/>
+      <c r="J8" s="242" t="s">
         <v>50</v>
       </c>
-      <c r="K8" s="253"/>
-      <c r="L8" s="253"/>
-      <c r="M8" s="253"/>
+      <c r="K8" s="242"/>
+      <c r="L8" s="242"/>
+      <c r="M8" s="242"/>
     </row>
     <row r="9" spans="1:13" s="44" customFormat="1">
-      <c r="A9" s="253"/>
-      <c r="B9" s="253"/>
-      <c r="C9" s="253"/>
-      <c r="D9" s="253"/>
-      <c r="E9" s="253"/>
-      <c r="F9" s="253"/>
+      <c r="A9" s="242"/>
+      <c r="B9" s="242"/>
+      <c r="C9" s="242"/>
+      <c r="D9" s="242"/>
+      <c r="E9" s="242"/>
+      <c r="F9" s="242"/>
       <c r="G9" s="63" t="s">
         <v>80</v>
       </c>
@@ -14881,24 +14870,24 @@
       <c r="L9" s="59" t="s">
         <v>82</v>
       </c>
-      <c r="M9" s="253"/>
+      <c r="M9" s="242"/>
     </row>
     <row r="10" spans="1:13" s="44" customFormat="1">
-      <c r="A10" s="252" t="s">
+      <c r="A10" s="241" t="s">
         <v>83</v>
       </c>
-      <c r="B10" s="252"/>
-      <c r="C10" s="252"/>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
-      <c r="M10" s="252"/>
+      <c r="B10" s="241"/>
+      <c r="C10" s="241"/>
+      <c r="D10" s="241"/>
+      <c r="E10" s="241"/>
+      <c r="F10" s="241"/>
+      <c r="G10" s="241"/>
+      <c r="H10" s="241"/>
+      <c r="I10" s="241"/>
+      <c r="J10" s="241"/>
+      <c r="K10" s="241"/>
+      <c r="L10" s="241"/>
+      <c r="M10" s="241"/>
     </row>
     <row r="11" spans="1:13" s="44" customFormat="1" ht="43.2" customHeight="1">
       <c r="A11" s="65" t="s">
@@ -15132,21 +15121,21 @@
       <c r="M17" s="181"/>
     </row>
     <row r="18" spans="1:13" s="44" customFormat="1">
-      <c r="A18" s="251" t="s">
+      <c r="A18" s="240" t="s">
         <v>95</v>
       </c>
-      <c r="B18" s="251"/>
-      <c r="C18" s="251"/>
-      <c r="D18" s="251"/>
-      <c r="E18" s="251"/>
-      <c r="F18" s="251"/>
-      <c r="G18" s="251"/>
-      <c r="H18" s="251"/>
-      <c r="I18" s="251"/>
-      <c r="J18" s="251"/>
-      <c r="K18" s="251"/>
-      <c r="L18" s="251"/>
-      <c r="M18" s="251"/>
+      <c r="B18" s="240"/>
+      <c r="C18" s="240"/>
+      <c r="D18" s="240"/>
+      <c r="E18" s="240"/>
+      <c r="F18" s="240"/>
+      <c r="G18" s="240"/>
+      <c r="H18" s="240"/>
+      <c r="I18" s="240"/>
+      <c r="J18" s="240"/>
+      <c r="K18" s="240"/>
+      <c r="L18" s="240"/>
+      <c r="M18" s="240"/>
     </row>
     <row r="19" spans="1:13" s="44" customFormat="1" ht="34.799999999999997" customHeight="1">
       <c r="A19" s="66" t="s">
@@ -15508,25 +15497,25 @@
       <c r="A1" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="257" t="s">
+      <c r="B1" s="246" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="247" t="s">
         <v>663</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="C2" s="247"/>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
     </row>
     <row r="3" spans="1:6" ht="16.8">
       <c r="A3" s="73"/>
@@ -15612,57 +15601,57 @@
     <row r="29" spans="1:12" hidden="1"/>
     <row r="30" spans="1:12" hidden="1"/>
     <row r="31" spans="1:12" ht="16.8">
-      <c r="A31" s="259" t="s">
+      <c r="A31" s="248" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="259" t="s">
+      <c r="B31" s="248" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="259" t="s">
+      <c r="C31" s="248" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="259" t="s">
+      <c r="D31" s="248" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="259" t="s">
+      <c r="E31" s="248" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="260" t="s">
+      <c r="F31" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260" t="s">
+      <c r="G31" s="249"/>
+      <c r="H31" s="249"/>
+      <c r="I31" s="249"/>
+      <c r="J31" s="249"/>
+      <c r="K31" s="249"/>
+      <c r="L31" s="249" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.8">
-      <c r="A32" s="259"/>
-      <c r="B32" s="259"/>
-      <c r="C32" s="259"/>
-      <c r="D32" s="259"/>
-      <c r="E32" s="259"/>
-      <c r="F32" s="260" t="s">
+      <c r="A32" s="248"/>
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="249" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260" t="s">
+      <c r="G32" s="249"/>
+      <c r="H32" s="249"/>
+      <c r="I32" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="J32" s="249"/>
+      <c r="K32" s="249"/>
+      <c r="L32" s="249"/>
     </row>
     <row r="33" spans="1:13" ht="36" customHeight="1">
-      <c r="A33" s="259"/>
-      <c r="B33" s="259"/>
-      <c r="C33" s="259"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
+      <c r="A33" s="248"/>
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
       <c r="F33" s="105" t="s">
         <v>80</v>
       </c>
@@ -15681,23 +15670,23 @@
       <c r="K33" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="L33" s="260"/>
+      <c r="L33" s="249"/>
     </row>
     <row r="34" spans="1:13" ht="16.8">
-      <c r="A34" s="261" t="s">
+      <c r="A34" s="250" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="262"/>
-      <c r="C34" s="262"/>
-      <c r="D34" s="262"/>
-      <c r="E34" s="262"/>
-      <c r="F34" s="262"/>
-      <c r="G34" s="262"/>
-      <c r="H34" s="262"/>
-      <c r="I34" s="262"/>
-      <c r="J34" s="262"/>
-      <c r="K34" s="262"/>
-      <c r="L34" s="263"/>
+      <c r="B34" s="251"/>
+      <c r="C34" s="251"/>
+      <c r="D34" s="251"/>
+      <c r="E34" s="251"/>
+      <c r="F34" s="251"/>
+      <c r="G34" s="251"/>
+      <c r="H34" s="251"/>
+      <c r="I34" s="251"/>
+      <c r="J34" s="251"/>
+      <c r="K34" s="251"/>
+      <c r="L34" s="252"/>
     </row>
     <row r="35" spans="1:13" ht="34.950000000000003" customHeight="1">
       <c r="A35" s="124" t="s">
@@ -15941,20 +15930,20 @@
       <c r="L42" s="118"/>
     </row>
     <row r="43" spans="1:13" ht="16.8">
-      <c r="A43" s="254" t="s">
+      <c r="A43" s="243" t="s">
         <v>129</v>
       </c>
-      <c r="B43" s="255"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="255"/>
-      <c r="H43" s="255"/>
-      <c r="I43" s="255"/>
-      <c r="J43" s="255"/>
-      <c r="K43" s="255"/>
-      <c r="L43" s="256"/>
+      <c r="B43" s="244"/>
+      <c r="C43" s="244"/>
+      <c r="D43" s="244"/>
+      <c r="E43" s="244"/>
+      <c r="F43" s="244"/>
+      <c r="G43" s="244"/>
+      <c r="H43" s="244"/>
+      <c r="I43" s="244"/>
+      <c r="J43" s="244"/>
+      <c r="K43" s="244"/>
+      <c r="L43" s="245"/>
     </row>
     <row r="44" spans="1:13" s="108" customFormat="1" ht="50.4">
       <c r="A44" s="125" t="s">
@@ -16229,25 +16218,25 @@
       <c r="A1" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="257" t="s">
+      <c r="B1" s="246" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
     </row>
     <row r="2" spans="1:6" ht="16.8">
       <c r="A2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="247" t="s">
         <v>664</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="C2" s="247"/>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
     </row>
     <row r="3" spans="1:6" ht="16.8">
       <c r="A3" s="73"/>
@@ -16310,57 +16299,57 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="16.8">
-      <c r="A31" s="271" t="s">
+      <c r="A31" s="253" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="271" t="s">
+      <c r="B31" s="253" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="271" t="s">
+      <c r="C31" s="253" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="271" t="s">
+      <c r="D31" s="253" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="271" t="s">
+      <c r="E31" s="253" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="264" t="s">
+      <c r="F31" s="254" t="s">
         <v>78</v>
       </c>
-      <c r="G31" s="264"/>
-      <c r="H31" s="264"/>
-      <c r="I31" s="264"/>
-      <c r="J31" s="264"/>
-      <c r="K31" s="264"/>
-      <c r="L31" s="264" t="s">
+      <c r="G31" s="254"/>
+      <c r="H31" s="254"/>
+      <c r="I31" s="254"/>
+      <c r="J31" s="254"/>
+      <c r="K31" s="254"/>
+      <c r="L31" s="254" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:12" ht="16.8">
-      <c r="A32" s="271"/>
-      <c r="B32" s="271"/>
-      <c r="C32" s="271"/>
-      <c r="D32" s="271"/>
-      <c r="E32" s="271"/>
-      <c r="F32" s="264" t="s">
+      <c r="A32" s="253"/>
+      <c r="B32" s="253"/>
+      <c r="C32" s="253"/>
+      <c r="D32" s="253"/>
+      <c r="E32" s="253"/>
+      <c r="F32" s="254" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="264"/>
-      <c r="H32" s="264"/>
-      <c r="I32" s="264" t="s">
+      <c r="G32" s="254"/>
+      <c r="H32" s="254"/>
+      <c r="I32" s="254" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="264"/>
-      <c r="K32" s="264"/>
-      <c r="L32" s="264"/>
-    </row>
-    <row r="33" spans="1:147" ht="33.6">
-      <c r="A33" s="271"/>
-      <c r="B33" s="271"/>
-      <c r="C33" s="271"/>
-      <c r="D33" s="271"/>
-      <c r="E33" s="271"/>
+      <c r="J32" s="254"/>
+      <c r="K32" s="254"/>
+      <c r="L32" s="254"/>
+    </row>
+    <row r="33" spans="1:147" ht="16.8">
+      <c r="A33" s="253"/>
+      <c r="B33" s="253"/>
+      <c r="C33" s="253"/>
+      <c r="D33" s="253"/>
+      <c r="E33" s="253"/>
       <c r="F33" s="126" t="s">
         <v>80</v>
       </c>
@@ -16379,23 +16368,23 @@
       <c r="K33" s="126" t="s">
         <v>82</v>
       </c>
-      <c r="L33" s="264"/>
+      <c r="L33" s="254"/>
     </row>
     <row r="34" spans="1:147" ht="16.8">
-      <c r="A34" s="265" t="s">
+      <c r="A34" s="255" t="s">
         <v>160</v>
       </c>
-      <c r="B34" s="266"/>
-      <c r="C34" s="266"/>
-      <c r="D34" s="266"/>
-      <c r="E34" s="266"/>
-      <c r="F34" s="266"/>
-      <c r="G34" s="266"/>
-      <c r="H34" s="266"/>
-      <c r="I34" s="266"/>
-      <c r="J34" s="266"/>
-      <c r="K34" s="266"/>
-      <c r="L34" s="267"/>
+      <c r="B34" s="256"/>
+      <c r="C34" s="256"/>
+      <c r="D34" s="256"/>
+      <c r="E34" s="256"/>
+      <c r="F34" s="256"/>
+      <c r="G34" s="256"/>
+      <c r="H34" s="256"/>
+      <c r="I34" s="256"/>
+      <c r="J34" s="256"/>
+      <c r="K34" s="256"/>
+      <c r="L34" s="257"/>
     </row>
     <row r="35" spans="1:147" ht="40.200000000000003" customHeight="1">
       <c r="A35" s="124" t="s">
@@ -16969,20 +16958,20 @@
       <c r="EQ44" s="108"/>
     </row>
     <row r="45" spans="1:147" s="104" customFormat="1" ht="16.8">
-      <c r="A45" s="268" t="s">
+      <c r="A45" s="258" t="s">
         <v>190</v>
       </c>
-      <c r="B45" s="269"/>
-      <c r="C45" s="269"/>
-      <c r="D45" s="269"/>
-      <c r="E45" s="269"/>
-      <c r="F45" s="269"/>
-      <c r="G45" s="269"/>
-      <c r="H45" s="269"/>
-      <c r="I45" s="269"/>
-      <c r="J45" s="269"/>
-      <c r="K45" s="269"/>
-      <c r="L45" s="270"/>
+      <c r="B45" s="259"/>
+      <c r="C45" s="259"/>
+      <c r="D45" s="259"/>
+      <c r="E45" s="259"/>
+      <c r="F45" s="259"/>
+      <c r="G45" s="259"/>
+      <c r="H45" s="259"/>
+      <c r="I45" s="259"/>
+      <c r="J45" s="259"/>
+      <c r="K45" s="259"/>
+      <c r="L45" s="260"/>
       <c r="M45" s="108"/>
       <c r="N45" s="108"/>
       <c r="O45" s="108"/>
@@ -18084,6 +18073,12 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="L31:L33"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A45:L45"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:K32"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A31:A33"/>
@@ -18091,12 +18086,6 @@
     <mergeCell ref="C31:C33"/>
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A45:L45"/>
-    <mergeCell ref="F31:K31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:K32"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="F46:F50 F35:F44 I46:I53 I35:I44" xr:uid="{00000000-0002-0000-0500-000000000000}">
@@ -18135,25 +18124,25 @@
       <c r="A1" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="257" t="s">
+      <c r="B1" s="246" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="257"/>
-      <c r="D1" s="257"/>
-      <c r="E1" s="257"/>
-      <c r="F1" s="257"/>
+      <c r="C1" s="246"/>
+      <c r="D1" s="246"/>
+      <c r="E1" s="246"/>
+      <c r="F1" s="246"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="258" t="s">
+      <c r="B2" s="247" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="258"/>
-      <c r="D2" s="258"/>
-      <c r="E2" s="258"/>
-      <c r="F2" s="258"/>
+      <c r="C2" s="247"/>
+      <c r="D2" s="247"/>
+      <c r="E2" s="247"/>
+      <c r="F2" s="247"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="73"/>
@@ -18239,57 +18228,57 @@
     <row r="29" spans="1:12" hidden="1"/>
     <row r="30" spans="1:12" hidden="1"/>
     <row r="31" spans="1:12">
-      <c r="A31" s="259" t="s">
+      <c r="A31" s="248" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="259" t="s">
+      <c r="B31" s="248" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="259" t="s">
+      <c r="C31" s="248" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="259" t="s">
+      <c r="D31" s="248" t="s">
         <v>76</v>
       </c>
-      <c r="E31" s="259" t="s">
+      <c r="E31" s="248" t="s">
         <v>77</v>
       </c>
-      <c r="F31" s="260" t="s">
+      <c r="F31" s="249" t="s">
         <v>78</v>
       </c>
-      <c r="G31" s="260"/>
-      <c r="H31" s="260"/>
-      <c r="I31" s="260"/>
-      <c r="J31" s="260"/>
-      <c r="K31" s="260"/>
-      <c r="L31" s="260" t="s">
+      <c r="G31" s="249"/>
+      <c r="H31" s="249"/>
+      <c r="I31" s="249"/>
+      <c r="J31" s="249"/>
+      <c r="K31" s="249"/>
+      <c r="L31" s="249" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:12">
-      <c r="A32" s="259"/>
-      <c r="B32" s="259"/>
-      <c r="C32" s="259"/>
-      <c r="D32" s="259"/>
-      <c r="E32" s="259"/>
-      <c r="F32" s="260" t="s">
+      <c r="A32" s="248"/>
+      <c r="B32" s="248"/>
+      <c r="C32" s="248"/>
+      <c r="D32" s="248"/>
+      <c r="E32" s="248"/>
+      <c r="F32" s="249" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="260"/>
-      <c r="H32" s="260"/>
-      <c r="I32" s="260" t="s">
+      <c r="G32" s="249"/>
+      <c r="H32" s="249"/>
+      <c r="I32" s="249" t="s">
         <v>50</v>
       </c>
-      <c r="J32" s="260"/>
-      <c r="K32" s="260"/>
-      <c r="L32" s="260"/>
+      <c r="J32" s="249"/>
+      <c r="K32" s="249"/>
+      <c r="L32" s="249"/>
     </row>
     <row r="33" spans="1:13" ht="33.6">
-      <c r="A33" s="259"/>
-      <c r="B33" s="259"/>
-      <c r="C33" s="259"/>
-      <c r="D33" s="259"/>
-      <c r="E33" s="259"/>
+      <c r="A33" s="248"/>
+      <c r="B33" s="248"/>
+      <c r="C33" s="248"/>
+      <c r="D33" s="248"/>
+      <c r="E33" s="248"/>
       <c r="F33" s="105" t="s">
         <v>80</v>
       </c>
@@ -18308,23 +18297,23 @@
       <c r="K33" s="105" t="s">
         <v>82</v>
       </c>
-      <c r="L33" s="260"/>
+      <c r="L33" s="249"/>
     </row>
     <row r="34" spans="1:13" ht="17.25" customHeight="1">
-      <c r="A34" s="261" t="s">
+      <c r="A34" s="250" t="s">
         <v>229</v>
       </c>
-      <c r="B34" s="262"/>
-      <c r="C34" s="262"/>
-      <c r="D34" s="262"/>
-      <c r="E34" s="262"/>
-      <c r="F34" s="262"/>
-      <c r="G34" s="262"/>
-      <c r="H34" s="262"/>
-      <c r="I34" s="262"/>
-      <c r="J34" s="262"/>
-      <c r="K34" s="262"/>
-      <c r="L34" s="263"/>
+      <c r="B34" s="251"/>
+      <c r="C34" s="251"/>
+      <c r="D34" s="251"/>
+      <c r="E34" s="251"/>
+      <c r="F34" s="251"/>
+      <c r="G34" s="251"/>
+      <c r="H34" s="251"/>
+      <c r="I34" s="251"/>
+      <c r="J34" s="251"/>
+      <c r="K34" s="251"/>
+      <c r="L34" s="252"/>
     </row>
     <row r="35" spans="1:13" ht="34.950000000000003" customHeight="1">
       <c r="A35" s="124" t="s">
@@ -18628,20 +18617,20 @@
       <c r="L44" s="73"/>
     </row>
     <row r="45" spans="1:13">
-      <c r="A45" s="272" t="s">
+      <c r="A45" s="261" t="s">
         <v>244</v>
       </c>
-      <c r="B45" s="273"/>
-      <c r="C45" s="273"/>
-      <c r="D45" s="273"/>
-      <c r="E45" s="273"/>
-      <c r="F45" s="273"/>
-      <c r="G45" s="273"/>
-      <c r="H45" s="273"/>
-      <c r="I45" s="273"/>
-      <c r="J45" s="273"/>
-      <c r="K45" s="273"/>
-      <c r="L45" s="274"/>
+      <c r="B45" s="262"/>
+      <c r="C45" s="262"/>
+      <c r="D45" s="262"/>
+      <c r="E45" s="262"/>
+      <c r="F45" s="262"/>
+      <c r="G45" s="262"/>
+      <c r="H45" s="262"/>
+      <c r="I45" s="262"/>
+      <c r="J45" s="262"/>
+      <c r="K45" s="262"/>
+      <c r="L45" s="263"/>
     </row>
     <row r="46" spans="1:13" ht="84">
       <c r="A46" s="125" t="s">
@@ -18933,6 +18922,11 @@
     </row>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="L31:L33"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:K32"/>
+    <mergeCell ref="A34:L34"/>
+    <mergeCell ref="A45:L45"/>
     <mergeCell ref="B1:F1"/>
     <mergeCell ref="B2:F2"/>
     <mergeCell ref="A31:A33"/>
@@ -18941,11 +18935,6 @@
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
     <mergeCell ref="F31:K31"/>
-    <mergeCell ref="L31:L33"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:K32"/>
-    <mergeCell ref="A34:L34"/>
-    <mergeCell ref="A45:L45"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" operator="equal" allowBlank="1" showErrorMessage="1" promptTitle="dfdf" sqref="F46:F53 I46:I53 F35:F44 I35:I44" xr:uid="{00000000-0002-0000-0600-000000000000}">
@@ -18985,26 +18974,26 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
@@ -19068,62 +19057,62 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="16.8">
-      <c r="A31" s="281" t="s">
+      <c r="A31" s="270" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="277" t="s">
+      <c r="B31" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="277" t="s">
+      <c r="C31" s="273" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="277" t="s">
+      <c r="D31" s="273" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="284" t="s">
+      <c r="E31" s="274" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="277" t="s">
+      <c r="F31" s="273" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="275" t="s">
+      <c r="G31" s="276" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="275"/>
-      <c r="I31" s="275"/>
-      <c r="J31" s="275"/>
-      <c r="K31" s="275"/>
-      <c r="L31" s="275"/>
-      <c r="M31" s="275" t="s">
+      <c r="H31" s="276"/>
+      <c r="I31" s="276"/>
+      <c r="J31" s="276"/>
+      <c r="K31" s="276"/>
+      <c r="L31" s="276"/>
+      <c r="M31" s="276" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="16.8">
-      <c r="A32" s="282"/>
-      <c r="B32" s="277"/>
-      <c r="C32" s="277"/>
-      <c r="D32" s="277"/>
-      <c r="E32" s="284"/>
-      <c r="F32" s="277"/>
-      <c r="G32" s="275" t="s">
+      <c r="A32" s="271"/>
+      <c r="B32" s="273"/>
+      <c r="C32" s="273"/>
+      <c r="D32" s="273"/>
+      <c r="E32" s="274"/>
+      <c r="F32" s="273"/>
+      <c r="G32" s="276" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="275"/>
-      <c r="I32" s="275"/>
-      <c r="J32" s="275" t="s">
+      <c r="H32" s="276"/>
+      <c r="I32" s="276"/>
+      <c r="J32" s="276" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="275"/>
-      <c r="L32" s="275"/>
-      <c r="M32" s="276"/>
+      <c r="K32" s="276"/>
+      <c r="L32" s="276"/>
+      <c r="M32" s="277"/>
     </row>
     <row r="33" spans="1:142" ht="16.8">
-      <c r="A33" s="283"/>
-      <c r="B33" s="277"/>
-      <c r="C33" s="277"/>
-      <c r="D33" s="277"/>
-      <c r="E33" s="284"/>
-      <c r="F33" s="277"/>
+      <c r="A33" s="272"/>
+      <c r="B33" s="273"/>
+      <c r="C33" s="273"/>
+      <c r="D33" s="273"/>
+      <c r="E33" s="274"/>
+      <c r="F33" s="273"/>
       <c r="G33" s="95" t="s">
         <v>80</v>
       </c>
@@ -19142,24 +19131,24 @@
       <c r="L33" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="M33" s="276"/>
+      <c r="M33" s="277"/>
     </row>
     <row r="34" spans="1:142" ht="16.8">
-      <c r="A34" s="278" t="s">
+      <c r="A34" s="264" t="s">
         <v>267</v>
       </c>
-      <c r="B34" s="279"/>
-      <c r="C34" s="279"/>
-      <c r="D34" s="279"/>
-      <c r="E34" s="279"/>
-      <c r="F34" s="279"/>
-      <c r="G34" s="279"/>
-      <c r="H34" s="279"/>
-      <c r="I34" s="279"/>
-      <c r="J34" s="279"/>
-      <c r="K34" s="279"/>
-      <c r="L34" s="279"/>
-      <c r="M34" s="280"/>
+      <c r="B34" s="265"/>
+      <c r="C34" s="265"/>
+      <c r="D34" s="265"/>
+      <c r="E34" s="265"/>
+      <c r="F34" s="265"/>
+      <c r="G34" s="265"/>
+      <c r="H34" s="265"/>
+      <c r="I34" s="265"/>
+      <c r="J34" s="265"/>
+      <c r="K34" s="265"/>
+      <c r="L34" s="265"/>
+      <c r="M34" s="266"/>
     </row>
     <row r="35" spans="1:142" s="120" customFormat="1" ht="40.200000000000003" customHeight="1">
       <c r="A35" s="124" t="s">
@@ -20720,21 +20709,21 @@
       <c r="EL44" s="121"/>
     </row>
     <row r="45" spans="1:142" ht="16.8">
-      <c r="A45" s="206" t="s">
+      <c r="A45" s="267" t="s">
         <v>288</v>
       </c>
-      <c r="B45" s="207"/>
-      <c r="C45" s="207"/>
-      <c r="D45" s="207"/>
-      <c r="E45" s="207"/>
-      <c r="F45" s="207"/>
-      <c r="G45" s="207"/>
-      <c r="H45" s="207"/>
-      <c r="I45" s="207"/>
-      <c r="J45" s="207"/>
-      <c r="K45" s="207"/>
-      <c r="L45" s="207"/>
-      <c r="M45" s="208"/>
+      <c r="B45" s="268"/>
+      <c r="C45" s="268"/>
+      <c r="D45" s="268"/>
+      <c r="E45" s="268"/>
+      <c r="F45" s="268"/>
+      <c r="G45" s="268"/>
+      <c r="H45" s="268"/>
+      <c r="I45" s="268"/>
+      <c r="J45" s="268"/>
+      <c r="K45" s="268"/>
+      <c r="L45" s="268"/>
+      <c r="M45" s="269"/>
     </row>
     <row r="46" spans="1:142" ht="67.2">
       <c r="A46" s="88" t="s">
@@ -20972,6 +20961,13 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="J32:L32"/>
+    <mergeCell ref="M31:M33"/>
+    <mergeCell ref="G31:L31"/>
+    <mergeCell ref="F31:F33"/>
     <mergeCell ref="A34:M34"/>
     <mergeCell ref="A45:M45"/>
     <mergeCell ref="A31:A33"/>
@@ -20979,13 +20975,6 @@
     <mergeCell ref="C31:C33"/>
     <mergeCell ref="D31:D33"/>
     <mergeCell ref="E31:E33"/>
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="J32:L32"/>
-    <mergeCell ref="M31:M33"/>
-    <mergeCell ref="G31:L31"/>
-    <mergeCell ref="F31:F33"/>
   </mergeCells>
   <phoneticPr fontId="38" type="noConversion"/>
   <dataValidations count="1">
@@ -21025,26 +21014,26 @@
       <c r="A1" s="93" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="200" t="s">
+      <c r="B1" s="204" t="s">
         <v>661</v>
       </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
-      <c r="E1" s="200"/>
-      <c r="F1" s="200"/>
+      <c r="C1" s="204"/>
+      <c r="D1" s="204"/>
+      <c r="E1" s="204"/>
+      <c r="F1" s="204"/>
       <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" ht="22.8">
       <c r="A2" s="93" t="s">
         <v>67</v>
       </c>
-      <c r="B2" s="201" t="s">
+      <c r="B2" s="275" t="s">
         <v>665</v>
       </c>
-      <c r="C2" s="201"/>
-      <c r="D2" s="201"/>
-      <c r="E2" s="201"/>
-      <c r="F2" s="201"/>
+      <c r="C2" s="275"/>
+      <c r="D2" s="275"/>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
       <c r="G2" s="41"/>
     </row>
     <row r="3" spans="1:7" ht="16.8">
@@ -21108,62 +21097,62 @@
       </c>
     </row>
     <row r="31" spans="1:13" ht="16.8">
-      <c r="A31" s="281" t="s">
+      <c r="A31" s="270" t="s">
         <v>73</v>
       </c>
-      <c r="B31" s="277" t="s">
+      <c r="B31" s="273" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="277" t="s">
+      <c r="C31" s="273" t="s">
         <v>102</v>
       </c>
-      <c r="D31" s="277" t="s">
+      <c r="D31" s="273" t="s">
         <v>75</v>
       </c>
-      <c r="E31" s="284" t="s">
+      <c r="E31" s="274" t="s">
         <v>76</v>
       </c>
-      <c r="F31" s="277" t="s">
+      <c r="F31" s="273" t="s">
         <v>77</v>
       </c>
-      <c r="G31" s="275" t="s">
+      <c r="G31" s="276" t="s">
         <v>78</v>
       </c>
-      <c r="H31" s="275"/>
-      <c r="I31" s="275"/>
-      <c r="J31" s="275"/>
-      <c r="K31" s="275"/>
-      <c r="L31" s="275"/>
-      <c r="M31" s="275" t="s">
+      <c r="H31" s="276"/>
+      <c r="I31" s="276"/>
+      <c r="J31" s="276"/>
+      <c r="K31" s="276"/>
+      <c r="L31" s="276"/>
+      <c r="M31" s="276" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="16.8">
-      <c r="A32" s="282"/>
-      <c r="B32" s="277"/>
-      <c r="C32" s="277"/>
-      <c r="D32" s="277"/>
-      <c r="E32" s="284"/>
-      <c r="F32" s="277"/>
-      <c r="G32" s="275" t="s">
+      <c r="A32" s="271"/>
+      <c r="B32" s="273"/>
+      <c r="C32" s="273"/>
+      <c r="D32" s="273"/>
+      <c r="E32" s="274"/>
+      <c r="F32" s="273"/>
+      <c r="G32" s="276" t="s">
         <v>49</v>
       </c>
-      <c r="H32" s="275"/>
-      <c r="I32" s="275"/>
-      <c r="J32" s="275" t="s">
+      <c r="H32" s="276"/>
+      <c r="I32" s="276"/>
+      <c r="J32" s="276" t="s">
         <v>50</v>
       </c>
-      <c r="K32" s="275"/>
-      <c r="L32" s="275"/>
-      <c r="M32" s="276"/>
+      <c r="K32" s="276"/>
+      <c r="L32" s="276"/>
+      <c r="M32" s="277"/>
     </row>
     <row r="33" spans="1:13" ht="16.8">
-      <c r="A33" s="283"/>
-      <c r="B33" s="277"/>
-      <c r="C33" s="277"/>
-      <c r="D33" s="277"/>
-      <c r="E33" s="284"/>
-      <c r="F33" s="277"/>
+      <c r="A33" s="272"/>
+      <c r="B33" s="273"/>
+      <c r="C33" s="273"/>
+      <c r="D33" s="273"/>
+      <c r="E33" s="274"/>
+      <c r="F33" s="273"/>
       <c r="G33" s="95" t="s">
         <v>80</v>
       </c>
@@ -21182,24 +21171,24 @@
       <c r="L33" s="95" t="s">
         <v>82</v>
       </c>
-      <c r="M33" s="276"/>
+      <c r="M33" s="277"/>
     </row>
     <row r="34" spans="1:13" ht="16.8">
-      <c r="A34" s="285" t="s">
+      <c r="A34" s="278" t="s">
         <v>317</v>
       </c>
-      <c r="B34" s="286"/>
-      <c r="C34" s="286"/>
-      <c r="D34" s="286"/>
-      <c r="E34" s="286"/>
-      <c r="F34" s="286"/>
-      <c r="G34" s="286"/>
-      <c r="H34" s="286"/>
-      <c r="I34" s="286"/>
-      <c r="J34" s="286"/>
-      <c r="K34" s="286"/>
-      <c r="L34" s="286"/>
-      <c r="M34" s="287"/>
+      <c r="B34" s="279"/>
+      <c r="C34" s="279"/>
+      <c r="D34" s="279"/>
+      <c r="E34" s="279"/>
+      <c r="F34" s="279"/>
+      <c r="G34" s="279"/>
+      <c r="H34" s="279"/>
+      <c r="I34" s="279"/>
+      <c r="J34" s="279"/>
+      <c r="K34" s="279"/>
+      <c r="L34" s="279"/>
+      <c r="M34" s="280"/>
     </row>
     <row r="35" spans="1:13" ht="40.200000000000003" customHeight="1">
       <c r="A35" s="118" t="s">
@@ -21448,23 +21437,23 @@
       <c r="M42" s="90"/>
     </row>
     <row r="43" spans="1:13" ht="16.8">
-      <c r="A43" s="254" t="s">
+      <c r="A43" s="243" t="s">
         <v>336</v>
       </c>
-      <c r="B43" s="255"/>
-      <c r="C43" s="255"/>
-      <c r="D43" s="255"/>
-      <c r="E43" s="255"/>
-      <c r="F43" s="255"/>
-      <c r="G43" s="255"/>
-      <c r="H43" s="255"/>
-      <c r="I43" s="255"/>
-      <c r="J43" s="255"/>
-      <c r="K43" s="255"/>
-      <c r="L43" s="255"/>
-      <c r="M43" s="256"/>
-    </row>
-    <row r="44" spans="1:13" ht="84">
+      <c r="B43" s="244"/>
+      <c r="C43" s="244"/>
+      <c r="D43" s="244"/>
+      <c r="E43" s="244"/>
+      <c r="F43" s="244"/>
+      <c r="G43" s="244"/>
+      <c r="H43" s="244"/>
+      <c r="I43" s="244"/>
+      <c r="J43" s="244"/>
+      <c r="K43" s="244"/>
+      <c r="L43" s="244"/>
+      <c r="M43" s="245"/>
+    </row>
+    <row r="44" spans="1:13" ht="67.2">
       <c r="A44" s="98" t="s">
         <v>337</v>
       </c>
@@ -21503,7 +21492,7 @@
       </c>
       <c r="M44" s="90"/>
     </row>
-    <row r="45" spans="1:13" ht="67.2">
+    <row r="45" spans="1:13" ht="50.4">
       <c r="A45" s="98" t="s">
         <v>340</v>
       </c>
@@ -21542,7 +21531,7 @@
       </c>
       <c r="M45" s="90"/>
     </row>
-    <row r="46" spans="1:13" ht="50.4">
+    <row r="46" spans="1:13" ht="33.6">
       <c r="A46" s="98" t="s">
         <v>345</v>
       </c>
@@ -21581,7 +21570,7 @@
       </c>
       <c r="M46" s="90"/>
     </row>
-    <row r="47" spans="1:13" ht="84">
+    <row r="47" spans="1:13" ht="67.2">
       <c r="A47" s="98" t="s">
         <v>349</v>
       </c>
@@ -21620,7 +21609,7 @@
       </c>
       <c r="M47" s="90"/>
     </row>
-    <row r="48" spans="1:13" ht="84">
+    <row r="48" spans="1:13" ht="67.2">
       <c r="A48" s="98" t="s">
         <v>353</v>
       </c>
@@ -21659,7 +21648,7 @@
       </c>
       <c r="M48" s="90"/>
     </row>
-    <row r="49" spans="1:13" ht="84">
+    <row r="49" spans="1:13" ht="67.2">
       <c r="A49" s="98" t="s">
         <v>357</v>
       </c>
